--- a/(枠)◯年度一式/管理月報/実施要領報告様式_(変更).xlsx
+++ b/(枠)◯年度一式/管理月報/実施要領報告様式_(変更).xlsx
@@ -5,12 +5,12 @@
   <workbookPr updateLinks="always" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\Desktop\R８年度一式\管理月報\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\ドキュメント\日報月報他\(枠)◯年度一式\管理月報\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A9E22E-E63D-4A7C-B022-8D1AD9D895BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD10E7C-F160-4B9F-9E9C-9A633807C6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2700" yWindow="90" windowWidth="15750" windowHeight="15480" activeTab="2" xr2:uid="{A1FB16B0-34AF-456D-9543-CB77EF9D5048}"/>
+    <workbookView xWindow="5610" yWindow="0" windowWidth="20535" windowHeight="15480" xr2:uid="{A1FB16B0-34AF-456D-9543-CB77EF9D5048}"/>
   </bookViews>
   <sheets>
     <sheet name="別記様式１" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,6 @@
     <externalReference r:id="rId13"/>
     <externalReference r:id="rId14"/>
     <externalReference r:id="rId15"/>
-    <externalReference r:id="rId16"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">別記様式１!$A$1:$O$100</definedName>
@@ -3142,9 +3141,141 @@
     <xf numFmtId="183" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3154,136 +3285,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -3297,54 +3344,6 @@
     </xf>
     <xf numFmtId="177" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3379,13 +3378,124 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Sheet1"/>
+      <sheetName val="A-1"/>
+      <sheetName val="A-2"/>
+      <sheetName val="B-1"/>
+      <sheetName val="収集（全般）"/>
+      <sheetName val="可燃"/>
+      <sheetName val="不燃・木くず・海岸清掃"/>
+      <sheetName val="ビン類"/>
+      <sheetName val="缶類"/>
+      <sheetName val="ペットボトル"/>
+      <sheetName val="紙類"/>
+      <sheetName val="粗大"/>
+      <sheetName val="産廃水産・医療・汚泥"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="2">
-          <cell r="C2">
-            <v>8</v>
+        <row r="9">
+          <cell r="E9">
+            <v>2027</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="C44">
+            <v>0</v>
+          </cell>
+          <cell r="D44">
+            <v>0</v>
+          </cell>
+          <cell r="E44">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="H45" t="str">
+            <v/>
+          </cell>
+          <cell r="L45" t="str">
+            <v/>
+          </cell>
+          <cell r="N45" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="H46">
+            <v>0</v>
+          </cell>
+          <cell r="L46">
+            <v>0</v>
+          </cell>
+          <cell r="N46">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="H47">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
+        <row r="45">
+          <cell r="C45">
+            <v>0</v>
+          </cell>
+          <cell r="D45">
+            <v>0</v>
+          </cell>
+          <cell r="E45">
+            <v>0</v>
+          </cell>
+          <cell r="F45">
+            <v>0</v>
+          </cell>
+          <cell r="G45">
+            <v>0</v>
+          </cell>
+          <cell r="H45">
+            <v>0</v>
+          </cell>
+          <cell r="I45">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4">
+        <row r="43">
+          <cell r="F43">
+            <v>0</v>
+          </cell>
+          <cell r="Q43">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9">
+        <row r="43">
+          <cell r="K43">
+            <v>0</v>
+          </cell>
+          <cell r="V43">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11">
+        <row r="43">
+          <cell r="F43">
+            <v>0</v>
+          </cell>
+          <cell r="U43">
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -3831,224 +3941,6 @@
 </file>
 
 <file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="A-1"/>
-      <sheetName val="A-2"/>
-      <sheetName val="B-1"/>
-      <sheetName val="収集（全般）"/>
-      <sheetName val="可燃"/>
-      <sheetName val="不燃・木くず・海岸清掃"/>
-      <sheetName val="ビン類"/>
-      <sheetName val="缶類"/>
-      <sheetName val="ペットボトル"/>
-      <sheetName val="紙類"/>
-      <sheetName val="粗大"/>
-      <sheetName val="産廃水産・医療・汚泥"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="13">
-          <cell r="C13"/>
-        </row>
-        <row r="14">
-          <cell r="C14"/>
-        </row>
-        <row r="15">
-          <cell r="C15"/>
-        </row>
-        <row r="16">
-          <cell r="C16"/>
-        </row>
-        <row r="17">
-          <cell r="C17"/>
-        </row>
-        <row r="18">
-          <cell r="C18"/>
-        </row>
-        <row r="19">
-          <cell r="C19"/>
-        </row>
-        <row r="20">
-          <cell r="C20"/>
-        </row>
-        <row r="21">
-          <cell r="C21"/>
-        </row>
-        <row r="22">
-          <cell r="C22"/>
-        </row>
-        <row r="23">
-          <cell r="C23"/>
-        </row>
-        <row r="24">
-          <cell r="C24"/>
-        </row>
-        <row r="25">
-          <cell r="C25"/>
-        </row>
-        <row r="26">
-          <cell r="C26"/>
-        </row>
-        <row r="27">
-          <cell r="C27"/>
-        </row>
-        <row r="28">
-          <cell r="C28"/>
-        </row>
-        <row r="29">
-          <cell r="C29"/>
-        </row>
-        <row r="30">
-          <cell r="C30"/>
-        </row>
-        <row r="31">
-          <cell r="C31"/>
-        </row>
-        <row r="32">
-          <cell r="C32"/>
-        </row>
-        <row r="33">
-          <cell r="C33"/>
-        </row>
-        <row r="34">
-          <cell r="C34"/>
-        </row>
-        <row r="35">
-          <cell r="C35"/>
-        </row>
-        <row r="36">
-          <cell r="C36"/>
-        </row>
-        <row r="37">
-          <cell r="C37"/>
-        </row>
-        <row r="38">
-          <cell r="C38"/>
-        </row>
-        <row r="39">
-          <cell r="C39"/>
-        </row>
-        <row r="40">
-          <cell r="C40"/>
-        </row>
-        <row r="41">
-          <cell r="C41"/>
-        </row>
-        <row r="42">
-          <cell r="C42"/>
-        </row>
-        <row r="43">
-          <cell r="C43"/>
-        </row>
-        <row r="44">
-          <cell r="C44">
-            <v>0</v>
-          </cell>
-          <cell r="D44">
-            <v>0</v>
-          </cell>
-          <cell r="E44">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="H45" t="str">
-            <v/>
-          </cell>
-          <cell r="L45" t="str">
-            <v/>
-          </cell>
-          <cell r="N45" t="str">
-            <v/>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="H46">
-            <v>0</v>
-          </cell>
-          <cell r="L46">
-            <v>0</v>
-          </cell>
-          <cell r="N46">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="H47">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="45">
-          <cell r="C45">
-            <v>0</v>
-          </cell>
-          <cell r="D45">
-            <v>0</v>
-          </cell>
-          <cell r="E45">
-            <v>0</v>
-          </cell>
-          <cell r="F45">
-            <v>0</v>
-          </cell>
-          <cell r="G45">
-            <v>0</v>
-          </cell>
-          <cell r="H45">
-            <v>0</v>
-          </cell>
-          <cell r="I45">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4">
-        <row r="43">
-          <cell r="F43">
-            <v>0</v>
-          </cell>
-          <cell r="Q43">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9">
-        <row r="43">
-          <cell r="K43">
-            <v>0</v>
-          </cell>
-          <cell r="V43">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11">
-        <row r="43">
-          <cell r="F43">
-            <v>0</v>
-          </cell>
-          <cell r="U43">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -6309,24 +6201,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="114" t="str">
-        <f>"令和"&amp;[1]Sheet1!$C$2&amp;"年度　ごみ焼却施設維持管理状況報告書"</f>
-        <v>令和8年度　ごみ焼却施設維持管理状況報告書</v>
-      </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
+      <c r="A1" s="82" t="str">
+        <f>"令和"&amp;'[1]A-1'!$E$9-2018&amp;"年度　ごみ焼却施設維持管理状況報告書"</f>
+        <v>令和9年度　ごみ焼却施設維持管理状況報告書</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="82"/>
+      <c r="M1" s="82"/>
+      <c r="N1" s="82"/>
+      <c r="O1" s="82"/>
     </row>
     <row r="2" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="O2" t="s">
@@ -6334,166 +6226,166 @@
       </c>
     </row>
     <row r="3" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="115" t="s">
+      <c r="A3" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="113"/>
-      <c r="C3" s="121" t="s">
+      <c r="B3" s="78"/>
+      <c r="C3" s="93" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="122"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="94"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="94"/>
+      <c r="K3" s="94"/>
+      <c r="L3" s="94"/>
+      <c r="M3" s="94"/>
+      <c r="N3" s="94"/>
+      <c r="O3" s="95"/>
     </row>
     <row r="4" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="115" t="s">
+      <c r="A4" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="113"/>
-      <c r="C4" s="81" t="s">
+      <c r="B4" s="78"/>
+      <c r="C4" s="87" t="s">
         <v>59</v>
       </c>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="103"/>
-      <c r="I4" s="103"/>
-      <c r="J4" s="103"/>
-      <c r="K4" s="103"/>
-      <c r="L4" s="103"/>
-      <c r="M4" s="103"/>
-      <c r="N4" s="103"/>
-      <c r="O4" s="104"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="89"/>
     </row>
     <row r="5" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="115" t="s">
+      <c r="A5" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="81" t="s">
+      <c r="B5" s="78"/>
+      <c r="C5" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="103"/>
-      <c r="J5" s="103"/>
-      <c r="K5" s="103"/>
-      <c r="L5" s="103"/>
-      <c r="M5" s="103"/>
-      <c r="N5" s="103"/>
-      <c r="O5" s="104"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="88"/>
+      <c r="F5" s="88"/>
+      <c r="G5" s="88"/>
+      <c r="H5" s="88"/>
+      <c r="I5" s="88"/>
+      <c r="J5" s="88"/>
+      <c r="K5" s="88"/>
+      <c r="L5" s="88"/>
+      <c r="M5" s="88"/>
+      <c r="N5" s="88"/>
+      <c r="O5" s="89"/>
     </row>
     <row r="6" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="120" t="s">
+      <c r="A6" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="80"/>
-      <c r="C6" s="119">
+      <c r="B6" s="92"/>
+      <c r="C6" s="90">
         <v>37070</v>
       </c>
-      <c r="D6" s="103"/>
-      <c r="E6" s="104"/>
-      <c r="F6" s="120" t="s">
+      <c r="D6" s="88"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="80"/>
-      <c r="H6" s="105" t="s">
+      <c r="G6" s="92"/>
+      <c r="H6" s="77" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="106"/>
-      <c r="J6" s="106"/>
-      <c r="K6" s="106"/>
-      <c r="L6" s="106"/>
-      <c r="M6" s="106"/>
-      <c r="N6" s="106"/>
-      <c r="O6" s="107"/>
+      <c r="I6" s="98"/>
+      <c r="J6" s="98"/>
+      <c r="K6" s="98"/>
+      <c r="L6" s="98"/>
+      <c r="M6" s="98"/>
+      <c r="N6" s="98"/>
+      <c r="O6" s="99"/>
       <c r="Q6" s="38"/>
     </row>
     <row r="7" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="105" t="s">
+      <c r="A7" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="113"/>
-      <c r="C7" s="116" t="s">
+      <c r="B7" s="78"/>
+      <c r="C7" s="84" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="117"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="105" t="s">
+      <c r="D7" s="85"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="77" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="113"/>
-      <c r="H7" s="105" t="s">
+      <c r="G7" s="78"/>
+      <c r="H7" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="I7" s="82"/>
-      <c r="J7" s="82"/>
-      <c r="K7" s="82"/>
-      <c r="L7" s="82"/>
-      <c r="M7" s="82"/>
-      <c r="N7" s="82"/>
-      <c r="O7" s="83"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="96"/>
+      <c r="K7" s="96"/>
+      <c r="L7" s="96"/>
+      <c r="M7" s="96"/>
+      <c r="N7" s="96"/>
+      <c r="O7" s="97"/>
       <c r="Q7" s="39"/>
     </row>
     <row r="8" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="105" t="s">
+      <c r="A8" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="113"/>
-      <c r="C8" s="81" t="s">
+      <c r="B8" s="78"/>
+      <c r="C8" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="82"/>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="105" t="s">
+      <c r="D8" s="96"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="97"/>
+      <c r="H8" s="77" t="s">
         <v>52</v>
       </c>
-      <c r="I8" s="83"/>
-      <c r="J8" s="81" t="s">
+      <c r="I8" s="97"/>
+      <c r="J8" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="K8" s="82"/>
-      <c r="L8" s="82"/>
-      <c r="M8" s="82"/>
-      <c r="N8" s="82"/>
-      <c r="O8" s="83"/>
+      <c r="K8" s="96"/>
+      <c r="L8" s="96"/>
+      <c r="M8" s="96"/>
+      <c r="N8" s="96"/>
+      <c r="O8" s="97"/>
       <c r="Q8" s="38"/>
     </row>
     <row r="9" spans="1:17" s="3" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="105" t="s">
+      <c r="A9" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="106"/>
-      <c r="C9" s="81" t="s">
+      <c r="B9" s="98"/>
+      <c r="C9" s="87" t="s">
         <v>80</v>
       </c>
-      <c r="D9" s="82"/>
-      <c r="E9" s="82"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="82"/>
-      <c r="H9" s="82"/>
-      <c r="I9" s="82"/>
-      <c r="J9" s="82"/>
-      <c r="K9" s="82"/>
-      <c r="L9" s="82"/>
-      <c r="M9" s="82"/>
-      <c r="N9" s="82"/>
-      <c r="O9" s="83"/>
+      <c r="D9" s="96"/>
+      <c r="E9" s="96"/>
+      <c r="F9" s="96"/>
+      <c r="G9" s="96"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="96"/>
+      <c r="J9" s="96"/>
+      <c r="K9" s="96"/>
+      <c r="L9" s="96"/>
+      <c r="M9" s="96"/>
+      <c r="N9" s="96"/>
+      <c r="O9" s="97"/>
       <c r="Q9" s="39"/>
     </row>
     <row r="10" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.15">
@@ -6519,8 +6411,8 @@
       </c>
     </row>
     <row r="12" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="109"/>
-      <c r="B12" s="110"/>
+      <c r="A12" s="101"/>
+      <c r="B12" s="102"/>
       <c r="C12" s="4" t="s">
         <v>64</v>
       </c>
@@ -6562,80 +6454,80 @@
       </c>
     </row>
     <row r="13" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="81" t="s">
+      <c r="A13" s="87" t="s">
         <v>89</v>
       </c>
-      <c r="B13" s="104"/>
+      <c r="B13" s="89"/>
       <c r="C13" s="30">
+        <f>[1]可燃!$F$43
++[1]紙類!$K$43</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="30">
         <f>[2]可燃!$F$43
 +[2]紙類!$K$43</f>
         <v>0</v>
       </c>
-      <c r="D13" s="30">
+      <c r="E13" s="30">
         <f>[3]可燃!$F$43
 +[3]紙類!$K$43</f>
         <v>0</v>
       </c>
-      <c r="E13" s="30">
+      <c r="F13" s="30">
         <f>[4]可燃!$F$43
 +[4]紙類!$K$43</f>
         <v>0</v>
       </c>
-      <c r="F13" s="30">
+      <c r="G13" s="30">
         <f>[5]可燃!$F$43
 +[5]紙類!$K$43</f>
         <v>0</v>
       </c>
-      <c r="G13" s="30">
+      <c r="H13" s="30">
         <f>[6]可燃!$F$43
 +[6]紙類!$K$43</f>
         <v>0</v>
       </c>
-      <c r="H13" s="30">
+      <c r="I13" s="30">
         <f>[7]可燃!$F$43
 +[7]紙類!$K$43</f>
         <v>0</v>
       </c>
-      <c r="I13" s="30">
+      <c r="J13" s="30">
         <f>[8]可燃!$F$43
 +[8]紙類!$K$43</f>
         <v>0</v>
       </c>
-      <c r="J13" s="30">
+      <c r="K13" s="30">
         <f>[9]可燃!$F$43
 +[9]紙類!$K$43</f>
         <v>0</v>
       </c>
-      <c r="K13" s="30">
+      <c r="L13" s="30">
         <f>[10]可燃!$F$43
 +[10]紙類!$K$43</f>
         <v>0</v>
       </c>
-      <c r="L13" s="30">
+      <c r="M13" s="30">
         <f>[11]可燃!$F$43
 +[11]紙類!$K$43</f>
         <v>0</v>
       </c>
-      <c r="M13" s="30">
+      <c r="N13" s="30">
         <f>[12]可燃!$F$43
 +[12]紙類!$K$43</f>
         <v>0</v>
       </c>
-      <c r="N13" s="30">
-        <f>[13]可燃!$F$43
-+[13]紙類!$K$43</f>
-        <v>0</v>
-      </c>
       <c r="O13" s="30">
         <f t="shared" ref="O13:O18" si="0">SUM(C13:N13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="108" t="s">
+      <c r="A14" s="100" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="104"/>
+      <c r="B14" s="89"/>
       <c r="C14" s="30">
         <f>SUM(C15:C17)</f>
         <v>0</v>
@@ -6695,63 +6587,63 @@
         <v>91</v>
       </c>
       <c r="C15" s="8">
+        <f>[1]可燃!$Q$43
++[1]紙類!$V$43</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="8">
         <f>[2]可燃!$Q$43
 +[2]紙類!$V$43</f>
         <v>0</v>
       </c>
-      <c r="D15" s="8">
+      <c r="E15" s="8">
         <f>[3]可燃!$Q$43
 +[3]紙類!$V$43</f>
         <v>0</v>
       </c>
-      <c r="E15" s="8">
+      <c r="F15" s="8">
         <f>[4]可燃!$Q$43
 +[4]紙類!$V$43</f>
         <v>0</v>
       </c>
-      <c r="F15" s="8">
+      <c r="G15" s="8">
         <f>[5]可燃!$Q$43
 +[5]紙類!$V$43</f>
         <v>0</v>
       </c>
-      <c r="G15" s="8">
+      <c r="H15" s="8">
         <f>[6]可燃!$Q$43
 +[6]紙類!$V$43</f>
         <v>0</v>
       </c>
-      <c r="H15" s="8">
+      <c r="I15" s="8">
         <f>[7]可燃!$Q$43
 +[7]紙類!$V$43</f>
         <v>0</v>
       </c>
-      <c r="I15" s="8">
+      <c r="J15" s="8">
         <f>[8]可燃!$Q$43
 +[8]紙類!$V$43</f>
         <v>0</v>
       </c>
-      <c r="J15" s="8">
+      <c r="K15" s="8">
         <f>[9]可燃!$Q$43
 +[9]紙類!$V$43</f>
         <v>0</v>
       </c>
-      <c r="K15" s="8">
+      <c r="L15" s="8">
         <f>[10]可燃!$Q$43
 +[10]紙類!$V$43</f>
         <v>0</v>
       </c>
-      <c r="L15" s="8">
+      <c r="M15" s="8">
         <f>[11]可燃!$Q$43
 +[11]紙類!$V$43</f>
         <v>0</v>
       </c>
-      <c r="M15" s="8">
+      <c r="N15" s="8">
         <f>[12]可燃!$Q$43
 +[12]紙類!$V$43</f>
-        <v>0</v>
-      </c>
-      <c r="N15" s="8">
-        <f>[13]可燃!$Q$43
-+[13]紙類!$V$43</f>
         <v>0</v>
       </c>
       <c r="O15" s="25">
@@ -6765,51 +6657,51 @@
         <v>86</v>
       </c>
       <c r="C16" s="51">
+        <f>[1]産廃水産・医療・汚泥!$U$43</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="51">
         <f>[2]産廃水産・医療・汚泥!$U$43</f>
         <v>0</v>
       </c>
-      <c r="D16" s="51">
+      <c r="E16" s="51">
         <f>[3]産廃水産・医療・汚泥!$U$43</f>
         <v>0</v>
       </c>
-      <c r="E16" s="51">
+      <c r="F16" s="51">
         <f>[4]産廃水産・医療・汚泥!$U$43</f>
         <v>0</v>
       </c>
-      <c r="F16" s="51">
+      <c r="G16" s="51">
         <f>[5]産廃水産・医療・汚泥!$U$43</f>
         <v>0</v>
       </c>
-      <c r="G16" s="51">
+      <c r="H16" s="51">
         <f>[6]産廃水産・医療・汚泥!$U$43</f>
         <v>0</v>
       </c>
-      <c r="H16" s="51">
+      <c r="I16" s="51">
         <f>[7]産廃水産・医療・汚泥!$U$43</f>
         <v>0</v>
       </c>
-      <c r="I16" s="51">
+      <c r="J16" s="51">
         <f>[8]産廃水産・医療・汚泥!$U$43</f>
         <v>0</v>
       </c>
-      <c r="J16" s="51">
+      <c r="K16" s="51">
         <f>[9]産廃水産・医療・汚泥!$U$43</f>
         <v>0</v>
       </c>
-      <c r="K16" s="51">
+      <c r="L16" s="51">
         <f>[10]産廃水産・医療・汚泥!$U$43</f>
         <v>0</v>
       </c>
-      <c r="L16" s="51">
+      <c r="M16" s="51">
         <f>[11]産廃水産・医療・汚泥!$U$43</f>
         <v>0</v>
       </c>
-      <c r="M16" s="51">
+      <c r="N16" s="51">
         <f>[12]産廃水産・医療・汚泥!$U$43</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="51">
-        <f>[13]産廃水産・医療・汚泥!$U$43</f>
         <v>0</v>
       </c>
       <c r="O16" s="9">
@@ -6823,51 +6715,51 @@
         <v>85</v>
       </c>
       <c r="C17" s="10">
+        <f>[1]産廃水産・医療・汚泥!$F$43</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="10">
         <f>[2]産廃水産・医療・汚泥!$F$43</f>
         <v>0</v>
       </c>
-      <c r="D17" s="10">
+      <c r="E17" s="10">
         <f>[3]産廃水産・医療・汚泥!$F$43</f>
         <v>0</v>
       </c>
-      <c r="E17" s="10">
+      <c r="F17" s="10">
         <f>[4]産廃水産・医療・汚泥!$F$43</f>
         <v>0</v>
       </c>
-      <c r="F17" s="10">
+      <c r="G17" s="10">
         <f>[5]産廃水産・医療・汚泥!$F$43</f>
         <v>0</v>
       </c>
-      <c r="G17" s="10">
+      <c r="H17" s="10">
         <f>[6]産廃水産・医療・汚泥!$F$43</f>
         <v>0</v>
       </c>
-      <c r="H17" s="10">
+      <c r="I17" s="10">
         <f>[7]産廃水産・医療・汚泥!$F$43</f>
         <v>0</v>
       </c>
-      <c r="I17" s="10">
+      <c r="J17" s="10">
         <f>[8]産廃水産・医療・汚泥!$F$43</f>
         <v>0</v>
       </c>
-      <c r="J17" s="10">
+      <c r="K17" s="10">
         <f>[9]産廃水産・医療・汚泥!$F$43</f>
         <v>0</v>
       </c>
-      <c r="K17" s="10">
+      <c r="L17" s="10">
         <f>[10]産廃水産・医療・汚泥!$F$43</f>
         <v>0</v>
       </c>
-      <c r="L17" s="10">
+      <c r="M17" s="10">
         <f>[11]産廃水産・医療・汚泥!$F$43</f>
         <v>0</v>
       </c>
-      <c r="M17" s="10">
+      <c r="N17" s="10">
         <f>[12]産廃水産・医療・汚泥!$F$43</f>
-        <v>0</v>
-      </c>
-      <c r="N17" s="10">
-        <f>[13]産廃水産・医療・汚泥!$F$43</f>
         <v>0</v>
       </c>
       <c r="O17" s="10">
@@ -6876,10 +6768,10 @@
       </c>
     </row>
     <row r="18" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="111" t="s">
+      <c r="A18" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="112"/>
+      <c r="B18" s="104"/>
       <c r="C18" s="30">
         <f>SUM(C13:C14)</f>
         <v>0</v>
@@ -6940,8 +6832,8 @@
       </c>
     </row>
     <row r="21" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="109"/>
-      <c r="B21" s="110"/>
+      <c r="A21" s="101"/>
+      <c r="B21" s="102"/>
       <c r="C21" s="4" t="s">
         <v>64</v>
       </c>
@@ -6983,58 +6875,58 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="100" t="s">
+      <c r="A22" s="79" t="s">
         <v>13</v>
       </c>
       <c r="B22" s="36" t="s">
         <v>49</v>
       </c>
       <c r="C22" s="25">
+        <f>'[1]A-1'!$C$44</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="25">
         <f>'[2]A-1'!$C$44</f>
         <v>0</v>
       </c>
-      <c r="D22" s="25">
+      <c r="E22" s="25">
         <f>'[3]A-1'!$C$44</f>
         <v>0</v>
       </c>
-      <c r="E22" s="25">
+      <c r="F22" s="25">
         <f>'[4]A-1'!$C$44</f>
         <v>0</v>
       </c>
-      <c r="F22" s="25">
+      <c r="G22" s="25">
         <f>'[5]A-1'!$C$44</f>
         <v>0</v>
       </c>
-      <c r="G22" s="25">
+      <c r="H22" s="25">
         <f>'[6]A-1'!$C$44</f>
         <v>0</v>
       </c>
-      <c r="H22" s="25">
+      <c r="I22" s="25">
         <f>'[7]A-1'!$C$44</f>
         <v>0</v>
       </c>
-      <c r="I22" s="25">
+      <c r="J22" s="25">
         <f>'[8]A-1'!$C$44</f>
         <v>0</v>
       </c>
-      <c r="J22" s="25">
+      <c r="K22" s="25">
         <f>'[9]A-1'!$C$44</f>
         <v>0</v>
       </c>
-      <c r="K22" s="25">
+      <c r="L22" s="25">
         <f>'[10]A-1'!$C$44</f>
         <v>0</v>
       </c>
-      <c r="L22" s="25">
+      <c r="M22" s="25">
         <f>'[11]A-1'!$C$44</f>
         <v>0</v>
       </c>
-      <c r="M22" s="25">
+      <c r="N22" s="25">
         <f>'[12]A-1'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="N22" s="25">
-        <f>'[13]A-1'!$C$44</f>
         <v>0</v>
       </c>
       <c r="O22" s="8">
@@ -7045,56 +6937,56 @@
       <c r="S22" s="3"/>
     </row>
     <row r="23" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="101"/>
+      <c r="A23" s="80"/>
       <c r="B23" s="35" t="s">
         <v>55</v>
       </c>
       <c r="C23" s="37">
+        <f>COUNTA('[1]A-1'!$C$13:$C$43)</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="37">
         <f>COUNTA('[2]A-1'!$C$13:$C$43)</f>
         <v>0</v>
       </c>
-      <c r="D23" s="37">
+      <c r="E23" s="37">
         <f>COUNTA('[3]A-1'!$C$13:$C$43)</f>
         <v>0</v>
       </c>
-      <c r="E23" s="37">
+      <c r="F23" s="37">
         <f>COUNTA('[4]A-1'!$C$13:$C$43)</f>
         <v>0</v>
       </c>
-      <c r="F23" s="37">
+      <c r="G23" s="37">
         <f>COUNTA('[5]A-1'!$C$13:$C$43)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="37">
+      <c r="H23" s="37">
         <f>COUNTA('[6]A-1'!$C$13:$C$43)</f>
         <v>0</v>
       </c>
-      <c r="H23" s="37">
+      <c r="I23" s="37">
         <f>COUNTA('[7]A-1'!$C$13:$C$43)</f>
         <v>0</v>
       </c>
-      <c r="I23" s="37">
+      <c r="J23" s="37">
         <f>COUNTA('[8]A-1'!$C$13:$C$43)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="37">
+      <c r="K23" s="37">
         <f>COUNTA('[9]A-1'!$C$13:$C$43)</f>
         <v>0</v>
       </c>
-      <c r="K23" s="37">
+      <c r="L23" s="37">
         <f>COUNTA('[10]A-1'!$C$13:$C$43)</f>
         <v>0</v>
       </c>
-      <c r="L23" s="37">
+      <c r="M23" s="37">
         <f>COUNTA('[11]A-1'!$C$13:$C$43)</f>
         <v>0</v>
       </c>
-      <c r="M23" s="37">
+      <c r="N23" s="37">
         <f>COUNTA('[12]A-1'!$C$13:$C$43)</f>
-        <v>0</v>
-      </c>
-      <c r="N23" s="37">
-        <f>COUNTA('[13]A-1'!$C$13:$C$43)</f>
         <v>0</v>
       </c>
       <c r="O23" s="65">
@@ -7104,7 +6996,7 @@
       <c r="S23" s="3"/>
     </row>
     <row r="24" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="101"/>
+      <c r="A24" s="80"/>
       <c r="B24" s="34" t="s">
         <v>48</v>
       </c>
@@ -7164,7 +7056,7 @@
       <c r="U24" s="3"/>
     </row>
     <row r="25" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="100" t="s">
+      <c r="A25" s="79" t="s">
         <v>0</v>
       </c>
       <c r="B25" s="36" t="s">
@@ -7224,7 +7116,7 @@
       </c>
     </row>
     <row r="26" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="101"/>
+      <c r="A26" s="80"/>
       <c r="B26" s="35" t="s">
         <v>56</v>
       </c>
@@ -7282,7 +7174,7 @@
       </c>
     </row>
     <row r="27" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="101"/>
+      <c r="A27" s="80"/>
       <c r="B27" s="7" t="s">
         <v>47</v>
       </c>
@@ -7342,56 +7234,56 @@
       <c r="Q27" s="3"/>
     </row>
     <row r="28" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="101"/>
+      <c r="A28" s="80"/>
       <c r="B28" s="33" t="s">
         <v>87</v>
       </c>
       <c r="C28" s="9">
+        <f>'[1]A-1'!$E$44</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="9">
         <f>'[2]A-1'!$E$44</f>
         <v>0</v>
       </c>
-      <c r="D28" s="9">
+      <c r="E28" s="9">
         <f>'[3]A-1'!$E$44</f>
         <v>0</v>
       </c>
-      <c r="E28" s="9">
+      <c r="F28" s="9">
         <f>'[4]A-1'!$E$44</f>
         <v>0</v>
       </c>
-      <c r="F28" s="9">
+      <c r="G28" s="9">
         <f>'[5]A-1'!$E$44</f>
         <v>0</v>
       </c>
-      <c r="G28" s="9">
+      <c r="H28" s="9">
         <f>'[6]A-1'!$E$44</f>
         <v>0</v>
       </c>
-      <c r="H28" s="9">
+      <c r="I28" s="9">
         <f>'[7]A-1'!$E$44</f>
         <v>0</v>
       </c>
-      <c r="I28" s="9">
+      <c r="J28" s="9">
         <f>'[8]A-1'!$E$44</f>
         <v>0</v>
       </c>
-      <c r="J28" s="9">
+      <c r="K28" s="9">
         <f>'[9]A-1'!$E$44</f>
         <v>0</v>
       </c>
-      <c r="K28" s="9">
+      <c r="L28" s="9">
         <f>'[10]A-1'!$E$44</f>
         <v>0</v>
       </c>
-      <c r="L28" s="9">
+      <c r="M28" s="9">
         <f>'[11]A-1'!$E$44</f>
         <v>0</v>
       </c>
-      <c r="M28" s="9">
+      <c r="N28" s="9">
         <f>'[12]A-1'!$E$44</f>
-        <v>0</v>
-      </c>
-      <c r="N28" s="9">
-        <f>'[13]A-1'!$E$44</f>
         <v>0</v>
       </c>
       <c r="O28" s="66">
@@ -7401,56 +7293,56 @@
       <c r="Q28" s="3"/>
     </row>
     <row r="29" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="102"/>
+      <c r="A29" s="81"/>
       <c r="B29" s="34" t="s">
         <v>88</v>
       </c>
       <c r="C29" s="24">
+        <f>'[1]A-1'!$D$44</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="24">
         <f>'[2]A-1'!$D$44</f>
         <v>0</v>
       </c>
-      <c r="D29" s="24">
+      <c r="E29" s="24">
         <f>'[3]A-1'!$D$44</f>
         <v>0</v>
       </c>
-      <c r="E29" s="24">
+      <c r="F29" s="24">
         <f>'[4]A-1'!$D$44</f>
         <v>0</v>
       </c>
-      <c r="F29" s="24">
+      <c r="G29" s="24">
         <f>'[5]A-1'!$D$44</f>
         <v>0</v>
       </c>
-      <c r="G29" s="24">
+      <c r="H29" s="24">
         <f>'[6]A-1'!$D$44</f>
         <v>0</v>
       </c>
-      <c r="H29" s="24">
+      <c r="I29" s="24">
         <f>'[7]A-1'!$D$44</f>
         <v>0</v>
       </c>
-      <c r="I29" s="24">
+      <c r="J29" s="24">
         <f>'[8]A-1'!$D$44</f>
         <v>0</v>
       </c>
-      <c r="J29" s="24">
+      <c r="K29" s="24">
         <f>'[9]A-1'!$D$44</f>
         <v>0</v>
       </c>
-      <c r="K29" s="24">
+      <c r="L29" s="24">
         <f>'[10]A-1'!$D$44</f>
         <v>0</v>
       </c>
-      <c r="L29" s="24">
+      <c r="M29" s="24">
         <f>'[11]A-1'!$D$44</f>
         <v>0</v>
       </c>
-      <c r="M29" s="24">
+      <c r="N29" s="24">
         <f>'[12]A-1'!$D$44</f>
-        <v>0</v>
-      </c>
-      <c r="N29" s="24">
-        <f>'[13]A-1'!$D$44</f>
         <v>0</v>
       </c>
       <c r="O29" s="10">
@@ -7465,8 +7357,8 @@
       </c>
     </row>
     <row r="32" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="95"/>
-      <c r="B32" s="96"/>
+      <c r="A32" s="106"/>
+      <c r="B32" s="107"/>
       <c r="C32" s="4" t="s">
         <v>64</v>
       </c>
@@ -7506,58 +7398,58 @@
       <c r="O32" s="4"/>
     </row>
     <row r="33" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="100" t="s">
+      <c r="A33" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="B33" s="97" t="s">
+      <c r="B33" s="108" t="s">
         <v>20</v>
       </c>
       <c r="C33" s="12">
+        <f>'[1]A-1'!$H$46</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="12">
         <f>'[2]A-1'!$H$46</f>
         <v>0</v>
       </c>
-      <c r="D33" s="12">
+      <c r="E33" s="12">
         <f>'[3]A-1'!$H$46</f>
         <v>0</v>
       </c>
-      <c r="E33" s="12">
+      <c r="F33" s="12">
         <f>'[4]A-1'!$H$46</f>
         <v>0</v>
       </c>
-      <c r="F33" s="12">
+      <c r="G33" s="12">
         <f>'[5]A-1'!$H$46</f>
         <v>0</v>
       </c>
-      <c r="G33" s="12">
+      <c r="H33" s="12">
         <f>'[6]A-1'!$H$46</f>
         <v>0</v>
       </c>
-      <c r="H33" s="12">
+      <c r="I33" s="12">
         <f>'[7]A-1'!$H$46</f>
         <v>0</v>
       </c>
-      <c r="I33" s="12">
+      <c r="J33" s="12">
         <f>'[8]A-1'!$H$46</f>
         <v>0</v>
       </c>
-      <c r="J33" s="12">
+      <c r="K33" s="12">
         <f>'[9]A-1'!$H$46</f>
         <v>0</v>
       </c>
-      <c r="K33" s="12">
+      <c r="L33" s="12">
         <f>'[10]A-1'!$H$46</f>
         <v>0</v>
       </c>
-      <c r="L33" s="12">
+      <c r="M33" s="12">
         <f>'[11]A-1'!$H$46</f>
         <v>0</v>
       </c>
-      <c r="M33" s="12">
+      <c r="N33" s="12">
         <f>'[12]A-1'!$H$46</f>
-        <v>0</v>
-      </c>
-      <c r="N33" s="12">
-        <f>'[13]A-1'!$H$46</f>
         <v>0</v>
       </c>
       <c r="O33" s="31" t="s">
@@ -7565,109 +7457,109 @@
       </c>
     </row>
     <row r="34" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="101"/>
-      <c r="B34" s="98"/>
+      <c r="A34" s="80"/>
+      <c r="B34" s="109"/>
       <c r="C34" s="14" t="str">
+        <f>'[1]A-1'!$H$45</f>
+        <v/>
+      </c>
+      <c r="D34" s="14" t="str">
         <f>'[2]A-1'!$H$45</f>
         <v/>
       </c>
-      <c r="D34" s="14" t="str">
+      <c r="E34" s="14" t="str">
         <f>'[3]A-1'!$H$45</f>
         <v/>
       </c>
-      <c r="E34" s="14" t="str">
+      <c r="F34" s="14" t="str">
         <f>'[4]A-1'!$H$45</f>
         <v/>
       </c>
-      <c r="F34" s="14" t="str">
+      <c r="G34" s="14" t="str">
         <f>'[5]A-1'!$H$45</f>
         <v/>
       </c>
-      <c r="G34" s="14" t="str">
+      <c r="H34" s="14" t="str">
         <f>'[6]A-1'!$H$45</f>
         <v/>
       </c>
-      <c r="H34" s="14" t="str">
+      <c r="I34" s="14" t="str">
         <f>'[7]A-1'!$H$45</f>
         <v/>
       </c>
-      <c r="I34" s="14" t="str">
+      <c r="J34" s="14" t="str">
         <f>'[8]A-1'!$H$45</f>
         <v/>
       </c>
-      <c r="J34" s="14" t="str">
+      <c r="K34" s="14" t="str">
         <f>'[9]A-1'!$H$45</f>
         <v/>
       </c>
-      <c r="K34" s="14" t="str">
+      <c r="L34" s="14" t="str">
         <f>'[10]A-1'!$H$45</f>
         <v/>
       </c>
-      <c r="L34" s="14" t="str">
+      <c r="M34" s="14" t="str">
         <f>'[11]A-1'!$H$45</f>
         <v/>
       </c>
-      <c r="M34" s="14" t="str">
+      <c r="N34" s="14" t="str">
         <f>'[12]A-1'!$H$45</f>
         <v/>
       </c>
-      <c r="N34" s="14" t="str">
-        <f>'[13]A-1'!$H$45</f>
-        <v/>
-      </c>
       <c r="O34" s="32" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="101"/>
-      <c r="B35" s="99"/>
+      <c r="A35" s="80"/>
+      <c r="B35" s="110"/>
       <c r="C35" s="16">
+        <f>'[1]A-1'!$H$47</f>
+        <v>0</v>
+      </c>
+      <c r="D35" s="16">
         <f>'[2]A-1'!$H$47</f>
         <v>0</v>
       </c>
-      <c r="D35" s="16">
+      <c r="E35" s="16">
         <f>'[3]A-1'!$H$47</f>
         <v>0</v>
       </c>
-      <c r="E35" s="16">
+      <c r="F35" s="16">
         <f>'[4]A-1'!$H$47</f>
         <v>0</v>
       </c>
-      <c r="F35" s="16">
+      <c r="G35" s="16">
         <f>'[5]A-1'!$H$47</f>
         <v>0</v>
       </c>
-      <c r="G35" s="16">
+      <c r="H35" s="16">
         <f>'[6]A-1'!$H$47</f>
         <v>0</v>
       </c>
-      <c r="H35" s="16">
+      <c r="I35" s="16">
         <f>'[7]A-1'!$H$47</f>
         <v>0</v>
       </c>
-      <c r="I35" s="16">
+      <c r="J35" s="16">
         <f>'[8]A-1'!$H$47</f>
         <v>0</v>
       </c>
-      <c r="J35" s="16">
+      <c r="K35" s="16">
         <f>'[9]A-1'!$H$47</f>
         <v>0</v>
       </c>
-      <c r="K35" s="16">
+      <c r="L35" s="16">
         <f>'[10]A-1'!$H$47</f>
         <v>0</v>
       </c>
-      <c r="L35" s="16">
+      <c r="M35" s="16">
         <f>'[11]A-1'!$H$47</f>
         <v>0</v>
       </c>
-      <c r="M35" s="16">
+      <c r="N35" s="16">
         <f>'[12]A-1'!$H$47</f>
-        <v>0</v>
-      </c>
-      <c r="N35" s="16">
-        <f>'[13]A-1'!$H$47</f>
         <v>0</v>
       </c>
       <c r="O35" s="17" t="s">
@@ -7675,56 +7567,56 @@
       </c>
     </row>
     <row r="36" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="101"/>
-      <c r="B36" s="97" t="s">
+      <c r="A36" s="80"/>
+      <c r="B36" s="108" t="s">
         <v>21</v>
       </c>
       <c r="C36" s="26">
+        <f>'[1]A-1'!$L$46</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="26">
         <f>'[2]A-1'!$L$46</f>
         <v>0</v>
       </c>
-      <c r="D36" s="26">
+      <c r="E36" s="26">
         <f>'[3]A-1'!$L$46</f>
         <v>0</v>
       </c>
-      <c r="E36" s="26">
+      <c r="F36" s="26">
         <f>'[4]A-1'!$L$46</f>
         <v>0</v>
       </c>
-      <c r="F36" s="26">
+      <c r="G36" s="26">
         <f>'[5]A-1'!$L$46</f>
         <v>0</v>
       </c>
-      <c r="G36" s="26">
+      <c r="H36" s="26">
         <f>'[6]A-1'!$L$46</f>
         <v>0</v>
       </c>
-      <c r="H36" s="26">
+      <c r="I36" s="26">
         <f>'[7]A-1'!$L$46</f>
         <v>0</v>
       </c>
-      <c r="I36" s="26">
+      <c r="J36" s="26">
         <f>'[8]A-1'!$L$46</f>
         <v>0</v>
       </c>
-      <c r="J36" s="26">
+      <c r="K36" s="26">
         <f>'[9]A-1'!$L$46</f>
         <v>0</v>
       </c>
-      <c r="K36" s="26">
+      <c r="L36" s="26">
         <f>'[10]A-1'!$L$46</f>
         <v>0</v>
       </c>
-      <c r="L36" s="26">
+      <c r="M36" s="26">
         <f>'[11]A-1'!$L$46</f>
         <v>0</v>
       </c>
-      <c r="M36" s="26">
+      <c r="N36" s="26">
         <f>'[12]A-1'!$L$46</f>
-        <v>0</v>
-      </c>
-      <c r="N36" s="26">
-        <f>'[13]A-1'!$L$46</f>
         <v>0</v>
       </c>
       <c r="O36" s="13" t="s">
@@ -7732,111 +7624,111 @@
       </c>
     </row>
     <row r="37" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="101"/>
-      <c r="B37" s="98"/>
+      <c r="A37" s="80"/>
+      <c r="B37" s="109"/>
       <c r="C37" s="40" t="str">
+        <f>'[1]A-1'!$L$45</f>
+        <v/>
+      </c>
+      <c r="D37" s="40" t="str">
         <f>'[2]A-1'!$L$45</f>
         <v/>
       </c>
-      <c r="D37" s="40" t="str">
+      <c r="E37" s="40" t="str">
         <f>'[3]A-1'!$L$45</f>
         <v/>
       </c>
-      <c r="E37" s="40" t="str">
+      <c r="F37" s="40" t="str">
         <f>'[4]A-1'!$L$45</f>
         <v/>
       </c>
-      <c r="F37" s="40" t="str">
+      <c r="G37" s="40" t="str">
         <f>'[5]A-1'!$L$45</f>
         <v/>
       </c>
-      <c r="G37" s="40" t="str">
+      <c r="H37" s="40" t="str">
         <f>'[6]A-1'!$L$45</f>
         <v/>
       </c>
-      <c r="H37" s="40" t="str">
+      <c r="I37" s="40" t="str">
         <f>'[7]A-1'!$L$45</f>
         <v/>
       </c>
-      <c r="I37" s="40" t="str">
+      <c r="J37" s="40" t="str">
         <f>'[8]A-1'!$L$45</f>
         <v/>
       </c>
-      <c r="J37" s="40" t="str">
+      <c r="K37" s="40" t="str">
         <f>'[9]A-1'!$L$45</f>
         <v/>
       </c>
-      <c r="K37" s="40" t="str">
+      <c r="L37" s="40" t="str">
         <f>'[10]A-1'!$L$45</f>
         <v/>
       </c>
-      <c r="L37" s="40" t="str">
+      <c r="M37" s="40" t="str">
         <f>'[11]A-1'!$L$45</f>
         <v/>
       </c>
-      <c r="M37" s="40" t="str">
+      <c r="N37" s="40" t="str">
         <f>'[12]A-1'!$L$45</f>
         <v/>
       </c>
-      <c r="N37" s="40" t="str">
-        <f>'[13]A-1'!$L$45</f>
-        <v/>
-      </c>
       <c r="O37" s="15" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="101"/>
-      <c r="B38" s="97" t="s">
+      <c r="A38" s="80"/>
+      <c r="B38" s="108" t="s">
         <v>19</v>
       </c>
       <c r="C38" s="12">
+        <f>'[1]A-1'!$N$46</f>
+        <v>0</v>
+      </c>
+      <c r="D38" s="12">
         <f>'[2]A-1'!$N$46</f>
         <v>0</v>
       </c>
-      <c r="D38" s="12">
+      <c r="E38" s="12">
         <f>'[3]A-1'!$N$46</f>
         <v>0</v>
       </c>
-      <c r="E38" s="12">
+      <c r="F38" s="12">
         <f>'[4]A-1'!$N$46</f>
         <v>0</v>
       </c>
-      <c r="F38" s="12">
+      <c r="G38" s="12">
         <f>'[5]A-1'!$N$46</f>
         <v>0</v>
       </c>
-      <c r="G38" s="12">
+      <c r="H38" s="12">
         <f>'[6]A-1'!$N$46</f>
         <v>0</v>
       </c>
-      <c r="H38" s="12">
+      <c r="I38" s="12">
         <f>'[7]A-1'!$N$46</f>
         <v>0</v>
       </c>
-      <c r="I38" s="12">
+      <c r="J38" s="12">
         <f>'[8]A-1'!$N$46</f>
         <v>0</v>
       </c>
-      <c r="J38" s="12">
+      <c r="K38" s="12">
         <f>'[9]A-1'!$N$46</f>
         <v>0</v>
       </c>
-      <c r="K38" s="12">
+      <c r="L38" s="12">
         <f>'[10]A-1'!$N$46</f>
         <v>0</v>
       </c>
-      <c r="L38" s="12">
+      <c r="M38" s="12">
         <f>'[11]A-1'!$N$46</f>
         <v>0</v>
       </c>
-      <c r="M38" s="12">
+      <c r="N38" s="12">
         <f>'[12]A-1'!$N$46</f>
-        <v>0</v>
-      </c>
-      <c r="N38" s="12">
-        <f>'[13]A-1'!$N$46</f>
         <v>0</v>
       </c>
       <c r="O38" s="13" t="s">
@@ -7844,54 +7736,54 @@
       </c>
     </row>
     <row r="39" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="102"/>
-      <c r="B39" s="99"/>
+      <c r="A39" s="81"/>
+      <c r="B39" s="110"/>
       <c r="C39" s="19" t="str">
+        <f>'[1]A-1'!$N$45</f>
+        <v/>
+      </c>
+      <c r="D39" s="19" t="str">
         <f>'[2]A-1'!$N$45</f>
         <v/>
       </c>
-      <c r="D39" s="19" t="str">
+      <c r="E39" s="19" t="str">
         <f>'[3]A-1'!$N$45</f>
         <v/>
       </c>
-      <c r="E39" s="19" t="str">
+      <c r="F39" s="19" t="str">
         <f>'[4]A-1'!$N$45</f>
         <v/>
       </c>
-      <c r="F39" s="19" t="str">
+      <c r="G39" s="19" t="str">
         <f>'[5]A-1'!$N$45</f>
         <v/>
       </c>
-      <c r="G39" s="19" t="str">
+      <c r="H39" s="19" t="str">
         <f>'[6]A-1'!$N$45</f>
         <v/>
       </c>
-      <c r="H39" s="19" t="str">
+      <c r="I39" s="19" t="str">
         <f>'[7]A-1'!$N$45</f>
         <v/>
       </c>
-      <c r="I39" s="19" t="str">
+      <c r="J39" s="19" t="str">
         <f>'[8]A-1'!$N$45</f>
         <v/>
       </c>
-      <c r="J39" s="19" t="str">
+      <c r="K39" s="19" t="str">
         <f>'[9]A-1'!$N$45</f>
         <v/>
       </c>
-      <c r="K39" s="19" t="str">
+      <c r="L39" s="19" t="str">
         <f>'[10]A-1'!$N$45</f>
         <v/>
       </c>
-      <c r="L39" s="19" t="str">
+      <c r="M39" s="19" t="str">
         <f>'[11]A-1'!$N$45</f>
         <v/>
       </c>
-      <c r="M39" s="19" t="str">
+      <c r="N39" s="19" t="str">
         <f>'[12]A-1'!$N$45</f>
-        <v/>
-      </c>
-      <c r="N39" s="19" t="str">
-        <f>'[13]A-1'!$N$45</f>
         <v/>
       </c>
       <c r="O39" s="52" t="s">
@@ -7902,151 +7794,151 @@
       <c r="A40" t="s">
         <v>96</v>
       </c>
-      <c r="F40" s="88" t="s">
+      <c r="F40" s="115" t="s">
         <v>189</v>
       </c>
-      <c r="G40" s="89"/>
-      <c r="H40" s="89"/>
-      <c r="I40" s="89"/>
-      <c r="J40" s="89"/>
-      <c r="K40" s="89"/>
-      <c r="L40" s="89"/>
+      <c r="G40" s="94"/>
+      <c r="H40" s="94"/>
+      <c r="I40" s="94"/>
+      <c r="J40" s="94"/>
+      <c r="K40" s="94"/>
+      <c r="L40" s="94"/>
     </row>
     <row r="41" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41"/>
-      <c r="B41" s="94"/>
-      <c r="C41" s="86" t="s">
+      <c r="B41" s="105"/>
+      <c r="C41" s="113" t="s">
         <v>97</v>
       </c>
-      <c r="D41" s="87"/>
-      <c r="E41" s="79" t="s">
+      <c r="D41" s="114"/>
+      <c r="E41" s="111" t="s">
         <v>98</v>
       </c>
-      <c r="F41" s="80"/>
-      <c r="G41" s="86" t="s">
+      <c r="F41" s="92"/>
+      <c r="G41" s="113" t="s">
         <v>99</v>
       </c>
-      <c r="H41" s="87"/>
-      <c r="I41" s="79" t="s">
+      <c r="H41" s="114"/>
+      <c r="I41" s="111" t="s">
         <v>100</v>
       </c>
-      <c r="J41" s="80"/>
-      <c r="K41" s="79" t="s">
+      <c r="J41" s="92"/>
+      <c r="K41" s="111" t="s">
         <v>101</v>
       </c>
-      <c r="L41" s="80"/>
-      <c r="M41" s="79" t="s">
+      <c r="L41" s="92"/>
+      <c r="M41" s="111" t="s">
         <v>185</v>
       </c>
-      <c r="N41" s="80"/>
+      <c r="N41" s="92"/>
     </row>
     <row r="42" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B42" s="94"/>
-      <c r="C42" s="90" t="s">
+      <c r="B42" s="105"/>
+      <c r="C42" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="D42" s="91"/>
-      <c r="E42" s="84" t="s">
+      <c r="D42" s="117"/>
+      <c r="E42" s="75" t="s">
         <v>103</v>
       </c>
-      <c r="F42" s="85"/>
-      <c r="G42" s="90" t="s">
+      <c r="F42" s="76"/>
+      <c r="G42" s="116" t="s">
         <v>104</v>
       </c>
-      <c r="H42" s="91"/>
-      <c r="I42" s="84" t="s">
+      <c r="H42" s="117"/>
+      <c r="I42" s="75" t="s">
         <v>105</v>
       </c>
-      <c r="J42" s="85"/>
-      <c r="K42" s="84" t="s">
+      <c r="J42" s="76"/>
+      <c r="K42" s="75" t="s">
         <v>106</v>
       </c>
-      <c r="L42" s="85"/>
-      <c r="M42" s="92" t="s">
+      <c r="L42" s="76"/>
+      <c r="M42" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="N42" s="93"/>
+      <c r="N42" s="119"/>
     </row>
     <row r="43" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="C43" s="75"/>
-      <c r="D43" s="75"/>
-      <c r="E43" s="75">
+      <c r="C43" s="112"/>
+      <c r="D43" s="112"/>
+      <c r="E43" s="112">
         <v>1E-3</v>
       </c>
-      <c r="F43" s="75"/>
-      <c r="G43" s="75">
+      <c r="F43" s="112"/>
+      <c r="G43" s="112">
         <v>16</v>
       </c>
-      <c r="H43" s="75"/>
-      <c r="I43" s="75">
+      <c r="H43" s="112"/>
+      <c r="I43" s="112">
         <v>0.03</v>
       </c>
-      <c r="J43" s="75"/>
-      <c r="K43" s="75">
+      <c r="J43" s="112"/>
+      <c r="K43" s="112">
         <v>86</v>
       </c>
-      <c r="L43" s="75"/>
-      <c r="M43" s="75">
+      <c r="L43" s="112"/>
+      <c r="M43" s="112">
         <v>0.28999999999999998</v>
       </c>
-      <c r="N43" s="75"/>
+      <c r="N43" s="112"/>
     </row>
     <row r="44" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="C44" s="75" t="s">
+      <c r="C44" s="112" t="s">
         <v>180</v>
       </c>
-      <c r="D44" s="75"/>
-      <c r="E44" s="75" t="s">
+      <c r="D44" s="112"/>
+      <c r="E44" s="112" t="s">
         <v>181</v>
       </c>
-      <c r="F44" s="75"/>
-      <c r="G44" s="75" t="s">
+      <c r="F44" s="112"/>
+      <c r="G44" s="112" t="s">
         <v>182</v>
       </c>
-      <c r="H44" s="75"/>
-      <c r="I44" s="75" t="s">
+      <c r="H44" s="112"/>
+      <c r="I44" s="112" t="s">
         <v>191</v>
       </c>
-      <c r="J44" s="75"/>
-      <c r="K44" s="75" t="s">
+      <c r="J44" s="112"/>
+      <c r="K44" s="112" t="s">
         <v>183</v>
       </c>
-      <c r="L44" s="75"/>
-      <c r="M44" s="75" t="s">
+      <c r="L44" s="112"/>
+      <c r="M44" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="N44" s="75"/>
+      <c r="N44" s="112"/>
     </row>
     <row r="45" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
         <v>159</v>
       </c>
-      <c r="E45" s="77" t="s">
+      <c r="E45" s="121" t="s">
         <v>187</v>
       </c>
-      <c r="F45" s="78"/>
-      <c r="G45" s="78"/>
-      <c r="H45" s="78"/>
-      <c r="I45" s="78"/>
-      <c r="J45" s="78"/>
-      <c r="K45" s="78"/>
+      <c r="F45" s="122"/>
+      <c r="G45" s="122"/>
+      <c r="H45" s="122"/>
+      <c r="I45" s="122"/>
+      <c r="J45" s="122"/>
+      <c r="K45" s="122"/>
     </row>
     <row r="46" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="64"/>
-      <c r="C46" s="76" t="s">
+      <c r="C46" s="120" t="s">
         <v>160</v>
       </c>
-      <c r="D46" s="75"/>
-      <c r="E46" s="76" t="s">
+      <c r="D46" s="112"/>
+      <c r="E46" s="120" t="s">
         <v>161</v>
       </c>
-      <c r="F46" s="75"/>
+      <c r="F46" s="112"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
@@ -8057,10 +7949,10 @@
       <c r="B47" s="63" t="s">
         <v>162</v>
       </c>
-      <c r="C47" s="75"/>
-      <c r="D47" s="75"/>
-      <c r="E47" s="75"/>
-      <c r="F47" s="75"/>
+      <c r="C47" s="112"/>
+      <c r="D47" s="112"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
       <c r="L47" s="70"/>
       <c r="M47" s="70"/>
     </row>
@@ -8278,6 +8170,54 @@
     </row>
   </sheetData>
   <mergeCells count="64">
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E45:K45"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="F40:L40"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C9:O9"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="M41:N41"/>
+    <mergeCell ref="M42:N42"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A33:A39"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="C4:O4"/>
+    <mergeCell ref="H6:O6"/>
+    <mergeCell ref="J8:O8"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="H8:I8"/>
     <mergeCell ref="E42:F42"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A25:A29"/>
@@ -8294,54 +8234,6 @@
     <mergeCell ref="C3:O3"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H7:O7"/>
-    <mergeCell ref="C4:O4"/>
-    <mergeCell ref="H6:O6"/>
-    <mergeCell ref="J8:O8"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="A33:A39"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="F40:L40"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C9:O9"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="M42:N42"/>
-    <mergeCell ref="M43:N43"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="E45:K45"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -8367,24 +8259,24 @@
       <c r="A1"/>
     </row>
     <row r="2" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="114" t="str">
-        <f>"令和"&amp;[1]Sheet1!$C$2&amp;"年度　最終処分場維持管理状況報告書"</f>
-        <v>令和8年度　最終処分場維持管理状況報告書</v>
-      </c>
-      <c r="B2" s="114"/>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="114"/>
-      <c r="J2" s="114"/>
-      <c r="K2" s="114"/>
-      <c r="L2" s="114"/>
-      <c r="M2" s="114"/>
-      <c r="N2" s="114"/>
-      <c r="O2" s="114"/>
+      <c r="A2" s="82" t="str">
+        <f>"令和"&amp;'[1]A-1'!$E$9-2018&amp;"年度　最終処分場維持管理状況報告書"</f>
+        <v>令和9年度　最終処分場維持管理状況報告書</v>
+      </c>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+      <c r="M2" s="82"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="82"/>
     </row>
     <row r="3" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="M3"/>
@@ -8393,167 +8285,167 @@
       </c>
     </row>
     <row r="4" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="115" t="s">
+      <c r="A4" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="113"/>
-      <c r="C4" s="121" t="s">
+      <c r="B4" s="78"/>
+      <c r="C4" s="93" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="89"/>
-      <c r="K4" s="89"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
-      <c r="N4" s="89"/>
-      <c r="O4" s="122"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="94"/>
+      <c r="J4" s="94"/>
+      <c r="K4" s="94"/>
+      <c r="L4" s="94"/>
+      <c r="M4" s="94"/>
+      <c r="N4" s="94"/>
+      <c r="O4" s="95"/>
     </row>
     <row r="5" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="115" t="s">
+      <c r="A5" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="81" t="s">
+      <c r="B5" s="78"/>
+      <c r="C5" s="87" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="103"/>
-      <c r="J5" s="103"/>
-      <c r="K5" s="103"/>
-      <c r="L5" s="103"/>
-      <c r="M5" s="103"/>
-      <c r="N5" s="103"/>
-      <c r="O5" s="104"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="88"/>
+      <c r="F5" s="88"/>
+      <c r="G5" s="88"/>
+      <c r="H5" s="88"/>
+      <c r="I5" s="88"/>
+      <c r="J5" s="88"/>
+      <c r="K5" s="88"/>
+      <c r="L5" s="88"/>
+      <c r="M5" s="88"/>
+      <c r="N5" s="88"/>
+      <c r="O5" s="89"/>
     </row>
     <row r="6" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="115" t="s">
+      <c r="A6" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="113"/>
-      <c r="C6" s="81" t="s">
+      <c r="B6" s="78"/>
+      <c r="C6" s="87" t="s">
         <v>201</v>
       </c>
-      <c r="D6" s="103"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="103"/>
-      <c r="G6" s="103"/>
-      <c r="H6" s="103"/>
-      <c r="I6" s="103"/>
-      <c r="J6" s="103"/>
-      <c r="K6" s="103"/>
-      <c r="L6" s="103"/>
-      <c r="M6" s="103"/>
-      <c r="N6" s="103"/>
-      <c r="O6" s="104"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="88"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="88"/>
+      <c r="I6" s="88"/>
+      <c r="J6" s="88"/>
+      <c r="K6" s="88"/>
+      <c r="L6" s="88"/>
+      <c r="M6" s="88"/>
+      <c r="N6" s="88"/>
+      <c r="O6" s="89"/>
     </row>
     <row r="7" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="120" t="s">
+      <c r="A7" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="80"/>
-      <c r="C7" s="140">
+      <c r="B7" s="92"/>
+      <c r="C7" s="123">
         <v>42527</v>
       </c>
-      <c r="D7" s="141"/>
-      <c r="E7" s="142"/>
-      <c r="F7" s="120" t="s">
+      <c r="D7" s="124"/>
+      <c r="E7" s="125"/>
+      <c r="F7" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="80"/>
-      <c r="H7" s="105" t="s">
+      <c r="G7" s="92"/>
+      <c r="H7" s="77" t="s">
         <v>195</v>
       </c>
-      <c r="I7" s="106"/>
-      <c r="J7" s="106"/>
-      <c r="K7" s="106"/>
-      <c r="L7" s="106"/>
-      <c r="M7" s="106"/>
-      <c r="N7" s="106"/>
-      <c r="O7" s="107"/>
+      <c r="I7" s="98"/>
+      <c r="J7" s="98"/>
+      <c r="K7" s="98"/>
+      <c r="L7" s="98"/>
+      <c r="M7" s="98"/>
+      <c r="N7" s="98"/>
+      <c r="O7" s="99"/>
     </row>
     <row r="8" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="76" t="s">
+      <c r="A8" s="120" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="75"/>
-      <c r="C8" s="116" t="s">
+      <c r="B8" s="112"/>
+      <c r="C8" s="84" t="s">
         <v>196</v>
       </c>
-      <c r="D8" s="117"/>
-      <c r="E8" s="118"/>
-      <c r="F8" s="76" t="s">
+      <c r="D8" s="85"/>
+      <c r="E8" s="86"/>
+      <c r="F8" s="120" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="75"/>
-      <c r="H8" s="105" t="s">
+      <c r="G8" s="112"/>
+      <c r="H8" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="I8" s="138"/>
-      <c r="J8" s="113"/>
-      <c r="K8" s="76" t="s">
+      <c r="I8" s="128"/>
+      <c r="J8" s="78"/>
+      <c r="K8" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="L8" s="75"/>
-      <c r="M8" s="105" t="s">
+      <c r="L8" s="112"/>
+      <c r="M8" s="77" t="s">
         <v>197</v>
       </c>
-      <c r="N8" s="138"/>
-      <c r="O8" s="113"/>
+      <c r="N8" s="128"/>
+      <c r="O8" s="78"/>
     </row>
     <row r="9" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="76" t="s">
+      <c r="A9" s="120" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="75"/>
-      <c r="C9" s="116" t="s">
+      <c r="B9" s="112"/>
+      <c r="C9" s="84" t="s">
         <v>199</v>
       </c>
-      <c r="D9" s="117"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="76" t="s">
+      <c r="D9" s="85"/>
+      <c r="E9" s="86"/>
+      <c r="F9" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="75"/>
-      <c r="H9" s="81" t="s">
+      <c r="G9" s="112"/>
+      <c r="H9" s="87" t="s">
         <v>198</v>
       </c>
-      <c r="I9" s="103"/>
-      <c r="J9" s="103"/>
-      <c r="K9" s="82"/>
-      <c r="L9" s="82"/>
-      <c r="M9" s="82"/>
-      <c r="N9" s="82"/>
-      <c r="O9" s="83"/>
+      <c r="I9" s="88"/>
+      <c r="J9" s="88"/>
+      <c r="K9" s="96"/>
+      <c r="L9" s="96"/>
+      <c r="M9" s="96"/>
+      <c r="N9" s="96"/>
+      <c r="O9" s="97"/>
     </row>
     <row r="10" spans="1:15" s="3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="105" t="s">
+      <c r="A10" s="77" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="106"/>
-      <c r="C10" s="121" t="s">
+      <c r="B10" s="98"/>
+      <c r="C10" s="93" t="s">
         <v>200</v>
       </c>
-      <c r="D10" s="88"/>
-      <c r="E10" s="88"/>
-      <c r="F10" s="88"/>
-      <c r="G10" s="88"/>
-      <c r="H10" s="88"/>
-      <c r="I10" s="88"/>
-      <c r="J10" s="88"/>
-      <c r="K10" s="88"/>
-      <c r="L10" s="88"/>
-      <c r="M10" s="88"/>
-      <c r="N10" s="88"/>
-      <c r="O10" s="139"/>
+      <c r="D10" s="115"/>
+      <c r="E10" s="115"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="115"/>
+      <c r="H10" s="115"/>
+      <c r="I10" s="115"/>
+      <c r="J10" s="115"/>
+      <c r="K10" s="115"/>
+      <c r="L10" s="115"/>
+      <c r="M10" s="115"/>
+      <c r="N10" s="115"/>
+      <c r="O10" s="129"/>
     </row>
     <row r="11" spans="1:15" s="3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2"/>
@@ -8569,8 +8461,8 @@
       </c>
     </row>
     <row r="13" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="109"/>
-      <c r="B13" s="110"/>
+      <c r="A13" s="101"/>
+      <c r="B13" s="102"/>
       <c r="C13" s="4" t="s">
         <v>12</v>
       </c>
@@ -8612,10 +8504,10 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="108" t="s">
+      <c r="A14" s="100" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="104"/>
+      <c r="B14" s="89"/>
       <c r="C14" s="30">
         <f>SUM(C15:C17)</f>
         <v>0</v>
@@ -8675,51 +8567,51 @@
         <v>57</v>
       </c>
       <c r="C15" s="8">
+        <f>'[1]B-1'!$C$45</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="8">
         <f>'[2]B-1'!$C$45</f>
         <v>0</v>
       </c>
-      <c r="D15" s="8">
+      <c r="E15" s="8">
         <f>'[3]B-1'!$C$45</f>
         <v>0</v>
       </c>
-      <c r="E15" s="8">
+      <c r="F15" s="8">
         <f>'[4]B-1'!$C$45</f>
         <v>0</v>
       </c>
-      <c r="F15" s="8">
+      <c r="G15" s="8">
         <f>'[5]B-1'!$C$45</f>
         <v>0</v>
       </c>
-      <c r="G15" s="8">
+      <c r="H15" s="8">
         <f>'[6]B-1'!$C$45</f>
         <v>0</v>
       </c>
-      <c r="H15" s="8">
+      <c r="I15" s="8">
         <f>'[7]B-1'!$C$45</f>
         <v>0</v>
       </c>
-      <c r="I15" s="8">
+      <c r="J15" s="8">
         <f>'[8]B-1'!$C$45</f>
         <v>0</v>
       </c>
-      <c r="J15" s="8">
+      <c r="K15" s="8">
         <f>'[9]B-1'!$C$45</f>
         <v>0</v>
       </c>
-      <c r="K15" s="8">
+      <c r="L15" s="8">
         <f>'[10]B-1'!$C$45</f>
         <v>0</v>
       </c>
-      <c r="L15" s="8">
+      <c r="M15" s="8">
         <f>'[11]B-1'!$C$45</f>
         <v>0</v>
       </c>
-      <c r="M15" s="8">
+      <c r="N15" s="8">
         <f>'[12]B-1'!$C$45</f>
-        <v>0</v>
-      </c>
-      <c r="N15" s="8">
-        <f>'[13]B-1'!$C$45</f>
         <v>0</v>
       </c>
       <c r="O15" s="8">
@@ -8733,75 +8625,75 @@
         <v>83</v>
       </c>
       <c r="C16" s="9">
+        <f>'[1]B-1'!$D$45
++'[1]B-1'!$E$45
++'[1]B-1'!$F$45</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="9">
         <f>'[2]B-1'!$D$45
 +'[2]B-1'!$E$45
 +'[2]B-1'!$F$45</f>
         <v>0</v>
       </c>
-      <c r="D16" s="9">
+      <c r="E16" s="9">
         <f>'[3]B-1'!$D$45
 +'[3]B-1'!$E$45
 +'[3]B-1'!$F$45</f>
         <v>0</v>
       </c>
-      <c r="E16" s="9">
+      <c r="F16" s="9">
         <f>'[4]B-1'!$D$45
 +'[4]B-1'!$E$45
 +'[4]B-1'!$F$45</f>
         <v>0</v>
       </c>
-      <c r="F16" s="9">
+      <c r="G16" s="9">
         <f>'[5]B-1'!$D$45
 +'[5]B-1'!$E$45
 +'[5]B-1'!$F$45</f>
         <v>0</v>
       </c>
-      <c r="G16" s="9">
+      <c r="H16" s="9">
         <f>'[6]B-1'!$D$45
 +'[6]B-1'!$E$45
 +'[6]B-1'!$F$45</f>
         <v>0</v>
       </c>
-      <c r="H16" s="9">
+      <c r="I16" s="9">
         <f>'[7]B-1'!$D$45
 +'[7]B-1'!$E$45
 +'[7]B-1'!$F$45</f>
         <v>0</v>
       </c>
-      <c r="I16" s="9">
+      <c r="J16" s="9">
         <f>'[8]B-1'!$D$45
 +'[8]B-1'!$E$45
 +'[8]B-1'!$F$45</f>
         <v>0</v>
       </c>
-      <c r="J16" s="9">
+      <c r="K16" s="9">
         <f>'[9]B-1'!$D$45
 +'[9]B-1'!$E$45
 +'[9]B-1'!$F$45</f>
         <v>0</v>
       </c>
-      <c r="K16" s="9">
+      <c r="L16" s="9">
         <f>'[10]B-1'!$D$45
 +'[10]B-1'!$E$45
 +'[10]B-1'!$F$45</f>
         <v>0</v>
       </c>
-      <c r="L16" s="9">
+      <c r="M16" s="9">
         <f>'[11]B-1'!$D$45
 +'[11]B-1'!$E$45
 +'[11]B-1'!$F$45</f>
         <v>0</v>
       </c>
-      <c r="M16" s="9">
+      <c r="N16" s="9">
         <f>'[12]B-1'!$D$45
 +'[12]B-1'!$E$45
 +'[12]B-1'!$F$45</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="9">
-        <f>'[13]B-1'!$D$45
-+'[13]B-1'!$E$45
-+'[13]B-1'!$F$45</f>
         <v>0</v>
       </c>
       <c r="O16" s="9">
@@ -8815,51 +8707,51 @@
         <v>85</v>
       </c>
       <c r="C17" s="24">
+        <f>'[1]B-1'!$G$45</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="24">
         <f>'[2]B-1'!$G$45</f>
         <v>0</v>
       </c>
-      <c r="D17" s="24">
+      <c r="E17" s="24">
         <f>'[3]B-1'!$G$45</f>
         <v>0</v>
       </c>
-      <c r="E17" s="24">
+      <c r="F17" s="24">
         <f>'[4]B-1'!$G$45</f>
         <v>0</v>
       </c>
-      <c r="F17" s="24">
+      <c r="G17" s="24">
         <f>'[5]B-1'!$G$45</f>
         <v>0</v>
       </c>
-      <c r="G17" s="24">
+      <c r="H17" s="24">
         <f>'[6]B-1'!$G$45</f>
         <v>0</v>
       </c>
-      <c r="H17" s="24">
+      <c r="I17" s="24">
         <f>'[7]B-1'!$G$45</f>
         <v>0</v>
       </c>
-      <c r="I17" s="24">
+      <c r="J17" s="24">
         <f>'[8]B-1'!$G$45</f>
         <v>0</v>
       </c>
-      <c r="J17" s="24">
+      <c r="K17" s="24">
         <f>'[9]B-1'!$G$45</f>
         <v>0</v>
       </c>
-      <c r="K17" s="24">
+      <c r="L17" s="24">
         <f>'[10]B-1'!$G$45</f>
         <v>0</v>
       </c>
-      <c r="L17" s="24">
+      <c r="M17" s="24">
         <f>'[11]B-1'!$G$45</f>
         <v>0</v>
       </c>
-      <c r="M17" s="24">
+      <c r="N17" s="24">
         <f>'[12]B-1'!$G$45</f>
-        <v>0</v>
-      </c>
-      <c r="N17" s="24">
-        <f>'[13]B-1'!$G$45</f>
         <v>0</v>
       </c>
       <c r="O17" s="24">
@@ -8868,56 +8760,56 @@
       </c>
     </row>
     <row r="18" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="81" t="s">
+      <c r="A18" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="83"/>
+      <c r="B18" s="97"/>
       <c r="C18" s="10">
+        <f>'[1]B-1'!$H$45</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="10">
         <f>'[2]B-1'!$H$45</f>
         <v>0</v>
       </c>
-      <c r="D18" s="10">
+      <c r="E18" s="10">
         <f>'[3]B-1'!$H$45</f>
         <v>0</v>
       </c>
-      <c r="E18" s="10">
+      <c r="F18" s="10">
         <f>'[4]B-1'!$H$45</f>
         <v>0</v>
       </c>
-      <c r="F18" s="10">
+      <c r="G18" s="10">
         <f>'[5]B-1'!$H$45</f>
         <v>0</v>
       </c>
-      <c r="G18" s="10">
+      <c r="H18" s="10">
         <f>'[6]B-1'!$H$45</f>
         <v>0</v>
       </c>
-      <c r="H18" s="10">
+      <c r="I18" s="10">
         <f>'[7]B-1'!$H$45</f>
         <v>0</v>
       </c>
-      <c r="I18" s="10">
+      <c r="J18" s="10">
         <f>'[8]B-1'!$H$45</f>
         <v>0</v>
       </c>
-      <c r="J18" s="10">
+      <c r="K18" s="10">
         <f>'[9]B-1'!$H$45</f>
         <v>0</v>
       </c>
-      <c r="K18" s="10">
+      <c r="L18" s="10">
         <f>'[10]B-1'!$H$45</f>
         <v>0</v>
       </c>
-      <c r="L18" s="10">
+      <c r="M18" s="10">
         <f>'[11]B-1'!$H$45</f>
         <v>0</v>
       </c>
-      <c r="M18" s="10">
+      <c r="N18" s="10">
         <f>'[12]B-1'!$H$45</f>
-        <v>0</v>
-      </c>
-      <c r="N18" s="10">
-        <f>'[13]B-1'!$H$45</f>
         <v>0</v>
       </c>
       <c r="O18" s="10">
@@ -8926,10 +8818,10 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="131" t="s">
+      <c r="A19" s="132" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="132"/>
+      <c r="B19" s="133"/>
       <c r="C19" s="25">
         <f>SUM(C15:C18)</f>
         <v>0</v>
@@ -8984,10 +8876,10 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="133" t="s">
+      <c r="A20" s="134" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="134"/>
+      <c r="B20" s="135"/>
       <c r="C20" s="46">
         <f>ROUND(C19*1.5,1)</f>
         <v>0</v>
@@ -9042,56 +8934,56 @@
       </c>
     </row>
     <row r="21" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="135" t="s">
+      <c r="A21" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="112"/>
+      <c r="B21" s="104"/>
       <c r="C21" s="47">
+        <f>'[1]B-1'!$I$45</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="47">
         <f>'[2]B-1'!$I$45</f>
         <v>0</v>
       </c>
-      <c r="D21" s="47">
+      <c r="E21" s="47">
         <f>'[3]B-1'!$I$45</f>
         <v>0</v>
       </c>
-      <c r="E21" s="47">
+      <c r="F21" s="47">
         <f>'[4]B-1'!$I$45</f>
         <v>0</v>
       </c>
-      <c r="F21" s="47">
+      <c r="G21" s="47">
         <f>'[5]B-1'!$I$45</f>
         <v>0</v>
       </c>
-      <c r="G21" s="47">
+      <c r="H21" s="47">
         <f>'[6]B-1'!$I$45</f>
         <v>0</v>
       </c>
-      <c r="H21" s="47">
+      <c r="I21" s="47">
         <f>'[7]B-1'!$I$45</f>
         <v>0</v>
       </c>
-      <c r="I21" s="47">
+      <c r="J21" s="47">
         <f>'[8]B-1'!$I$45</f>
         <v>0</v>
       </c>
-      <c r="J21" s="47">
+      <c r="K21" s="47">
         <f>'[9]B-1'!$I$45</f>
         <v>0</v>
       </c>
-      <c r="K21" s="47">
+      <c r="L21" s="47">
         <f>'[10]B-1'!$I$45</f>
         <v>0</v>
       </c>
-      <c r="L21" s="47">
+      <c r="M21" s="47">
         <f>'[11]B-1'!$I$45</f>
         <v>0</v>
       </c>
-      <c r="M21" s="47">
+      <c r="N21" s="47">
         <f>'[12]B-1'!$I$45</f>
-        <v>0</v>
-      </c>
-      <c r="N21" s="47">
-        <f>'[13]B-1'!$I$45</f>
         <v>0</v>
       </c>
       <c r="O21" s="47">
@@ -9100,10 +8992,10 @@
       </c>
     </row>
     <row r="22" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="135" t="s">
+      <c r="A22" s="136" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="112"/>
+      <c r="B22" s="104"/>
       <c r="C22" s="47">
         <f>SUM(C20:C21)</f>
         <v>0</v>
@@ -9162,13 +9054,13 @@
         <v>188</v>
       </c>
       <c r="B23"/>
-      <c r="D23" s="130"/>
-      <c r="E23" s="130"/>
-      <c r="K23" s="136"/>
-      <c r="L23" s="137"/>
-      <c r="M23" s="137"/>
-      <c r="N23" s="136"/>
-      <c r="O23" s="137"/>
+      <c r="D23" s="131"/>
+      <c r="E23" s="131"/>
+      <c r="K23" s="126"/>
+      <c r="L23" s="127"/>
+      <c r="M23" s="127"/>
+      <c r="N23" s="126"/>
+      <c r="O23" s="127"/>
     </row>
     <row r="24" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="25" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -9177,8 +9069,8 @@
       </c>
     </row>
     <row r="26" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="95"/>
-      <c r="B26" s="96"/>
+      <c r="A26" s="106"/>
+      <c r="B26" s="107"/>
       <c r="C26" s="4" t="s">
         <v>12</v>
       </c>
@@ -9220,7 +9112,7 @@
       </c>
     </row>
     <row r="27" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="129" t="s">
+      <c r="A27" s="130" t="s">
         <v>28</v>
       </c>
       <c r="B27" s="11" t="s">
@@ -9244,7 +9136,7 @@
       </c>
     </row>
     <row r="28" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="101"/>
+      <c r="A28" s="80"/>
       <c r="B28" s="28" t="s">
         <v>36</v>
       </c>
@@ -9266,7 +9158,7 @@
       </c>
     </row>
     <row r="29" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="101"/>
+      <c r="A29" s="80"/>
       <c r="B29" s="27" t="s">
         <v>38</v>
       </c>
@@ -9288,7 +9180,7 @@
       </c>
     </row>
     <row r="30" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="129" t="s">
+      <c r="A30" s="130" t="s">
         <v>29</v>
       </c>
       <c r="B30" s="11" t="s">
@@ -9312,7 +9204,7 @@
       </c>
     </row>
     <row r="31" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="101"/>
+      <c r="A31" s="80"/>
       <c r="B31" s="28" t="s">
         <v>36</v>
       </c>
@@ -9334,7 +9226,7 @@
       </c>
     </row>
     <row r="32" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="102"/>
+      <c r="A32" s="81"/>
       <c r="B32" s="55" t="s">
         <v>38</v>
       </c>
@@ -9368,139 +9260,139 @@
       <c r="I35" s="18"/>
     </row>
     <row r="36" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="128" t="s">
+      <c r="A36" s="138" t="s">
         <v>92</v>
       </c>
-      <c r="B36" s="128"/>
-      <c r="C36" s="128"/>
-      <c r="D36" s="128"/>
-      <c r="E36" s="128"/>
-      <c r="F36" s="128"/>
-      <c r="G36" s="128"/>
-      <c r="H36" s="128"/>
-      <c r="I36" s="128"/>
-      <c r="J36" s="128"/>
-      <c r="K36" s="128"/>
-      <c r="L36" s="128"/>
-      <c r="M36" s="128"/>
-      <c r="N36" s="128"/>
+      <c r="B36" s="138"/>
+      <c r="C36" s="138"/>
+      <c r="D36" s="138"/>
+      <c r="E36" s="138"/>
+      <c r="F36" s="138"/>
+      <c r="G36" s="138"/>
+      <c r="H36" s="138"/>
+      <c r="I36" s="138"/>
+      <c r="J36" s="138"/>
+      <c r="K36" s="138"/>
+      <c r="L36" s="138"/>
+      <c r="M36" s="138"/>
+      <c r="N36" s="138"/>
       <c r="O36" s="57"/>
     </row>
     <row r="37" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="76" t="s">
+      <c r="A37" s="120" t="s">
         <v>95</v>
       </c>
-      <c r="B37" s="75"/>
-      <c r="C37" s="76" t="s">
+      <c r="B37" s="112"/>
+      <c r="C37" s="120" t="s">
         <v>93</v>
       </c>
-      <c r="D37" s="75"/>
-      <c r="E37" s="75"/>
-      <c r="F37" s="76" t="s">
+      <c r="D37" s="112"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="120" t="s">
         <v>94</v>
       </c>
-      <c r="G37" s="76"/>
-      <c r="H37" s="76"/>
-      <c r="I37" s="76"/>
-      <c r="J37" s="76"/>
-      <c r="K37" s="76"/>
-      <c r="L37" s="76"/>
-      <c r="M37" s="76"/>
-      <c r="N37" s="76"/>
-      <c r="O37" s="76"/>
+      <c r="G37" s="120"/>
+      <c r="H37" s="120"/>
+      <c r="I37" s="120"/>
+      <c r="J37" s="120"/>
+      <c r="K37" s="120"/>
+      <c r="L37" s="120"/>
+      <c r="M37" s="120"/>
+      <c r="N37" s="120"/>
+      <c r="O37" s="120"/>
     </row>
     <row r="38" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="127">
+      <c r="A38" s="137">
         <v>45036</v>
       </c>
-      <c r="B38" s="127"/>
-      <c r="C38" s="123"/>
-      <c r="D38" s="123"/>
-      <c r="E38" s="123"/>
-      <c r="F38" s="124" t="s">
+      <c r="B38" s="137"/>
+      <c r="C38" s="139"/>
+      <c r="D38" s="139"/>
+      <c r="E38" s="139"/>
+      <c r="F38" s="140" t="s">
         <v>179</v>
       </c>
-      <c r="G38" s="125"/>
-      <c r="H38" s="125"/>
-      <c r="I38" s="125"/>
-      <c r="J38" s="125"/>
-      <c r="K38" s="125"/>
-      <c r="L38" s="125"/>
-      <c r="M38" s="125"/>
-      <c r="N38" s="125"/>
-      <c r="O38" s="126"/>
+      <c r="G38" s="141"/>
+      <c r="H38" s="141"/>
+      <c r="I38" s="141"/>
+      <c r="J38" s="141"/>
+      <c r="K38" s="141"/>
+      <c r="L38" s="141"/>
+      <c r="M38" s="141"/>
+      <c r="N38" s="141"/>
+      <c r="O38" s="142"/>
     </row>
     <row r="39" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="127">
+      <c r="A39" s="137">
         <v>45108</v>
       </c>
-      <c r="B39" s="127"/>
-      <c r="C39" s="123"/>
-      <c r="D39" s="123"/>
-      <c r="E39" s="123"/>
-      <c r="F39" s="124" t="s">
+      <c r="B39" s="137"/>
+      <c r="C39" s="139"/>
+      <c r="D39" s="139"/>
+      <c r="E39" s="139"/>
+      <c r="F39" s="140" t="s">
         <v>179</v>
       </c>
-      <c r="G39" s="125"/>
-      <c r="H39" s="125"/>
-      <c r="I39" s="125"/>
-      <c r="J39" s="125"/>
-      <c r="K39" s="125"/>
-      <c r="L39" s="125"/>
-      <c r="M39" s="125"/>
-      <c r="N39" s="125"/>
-      <c r="O39" s="126"/>
+      <c r="G39" s="141"/>
+      <c r="H39" s="141"/>
+      <c r="I39" s="141"/>
+      <c r="J39" s="141"/>
+      <c r="K39" s="141"/>
+      <c r="L39" s="141"/>
+      <c r="M39" s="141"/>
+      <c r="N39" s="141"/>
+      <c r="O39" s="142"/>
     </row>
     <row r="40" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="76"/>
-      <c r="B40" s="76"/>
-      <c r="C40" s="123"/>
-      <c r="D40" s="123"/>
-      <c r="E40" s="123"/>
-      <c r="F40" s="123"/>
-      <c r="G40" s="123"/>
-      <c r="H40" s="123"/>
-      <c r="I40" s="123"/>
-      <c r="J40" s="123"/>
-      <c r="K40" s="123"/>
-      <c r="L40" s="123"/>
-      <c r="M40" s="123"/>
-      <c r="N40" s="123"/>
-      <c r="O40" s="123"/>
+      <c r="A40" s="120"/>
+      <c r="B40" s="120"/>
+      <c r="C40" s="139"/>
+      <c r="D40" s="139"/>
+      <c r="E40" s="139"/>
+      <c r="F40" s="139"/>
+      <c r="G40" s="139"/>
+      <c r="H40" s="139"/>
+      <c r="I40" s="139"/>
+      <c r="J40" s="139"/>
+      <c r="K40" s="139"/>
+      <c r="L40" s="139"/>
+      <c r="M40" s="139"/>
+      <c r="N40" s="139"/>
+      <c r="O40" s="139"/>
     </row>
     <row r="41" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="76"/>
-      <c r="B41" s="76"/>
-      <c r="C41" s="123"/>
-      <c r="D41" s="123"/>
-      <c r="E41" s="123"/>
-      <c r="F41" s="123"/>
-      <c r="G41" s="123"/>
-      <c r="H41" s="123"/>
-      <c r="I41" s="123"/>
-      <c r="J41" s="123"/>
-      <c r="K41" s="123"/>
-      <c r="L41" s="123"/>
-      <c r="M41" s="123"/>
-      <c r="N41" s="123"/>
-      <c r="O41" s="123"/>
+      <c r="A41" s="120"/>
+      <c r="B41" s="120"/>
+      <c r="C41" s="139"/>
+      <c r="D41" s="139"/>
+      <c r="E41" s="139"/>
+      <c r="F41" s="139"/>
+      <c r="G41" s="139"/>
+      <c r="H41" s="139"/>
+      <c r="I41" s="139"/>
+      <c r="J41" s="139"/>
+      <c r="K41" s="139"/>
+      <c r="L41" s="139"/>
+      <c r="M41" s="139"/>
+      <c r="N41" s="139"/>
+      <c r="O41" s="139"/>
     </row>
     <row r="42" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="76"/>
-      <c r="B42" s="76"/>
-      <c r="C42" s="123"/>
-      <c r="D42" s="123"/>
-      <c r="E42" s="123"/>
-      <c r="F42" s="123"/>
-      <c r="G42" s="123"/>
-      <c r="H42" s="123"/>
-      <c r="I42" s="123"/>
-      <c r="J42" s="123"/>
-      <c r="K42" s="123"/>
-      <c r="L42" s="123"/>
-      <c r="M42" s="123"/>
-      <c r="N42" s="123"/>
-      <c r="O42" s="123"/>
+      <c r="A42" s="120"/>
+      <c r="B42" s="120"/>
+      <c r="C42" s="139"/>
+      <c r="D42" s="139"/>
+      <c r="E42" s="139"/>
+      <c r="F42" s="139"/>
+      <c r="G42" s="139"/>
+      <c r="H42" s="139"/>
+      <c r="I42" s="139"/>
+      <c r="J42" s="139"/>
+      <c r="K42" s="139"/>
+      <c r="L42" s="139"/>
+      <c r="M42" s="139"/>
+      <c r="N42" s="139"/>
+      <c r="O42" s="139"/>
     </row>
     <row r="43" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43"/>
@@ -9526,6 +9418,45 @@
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="F41:O41"/>
+    <mergeCell ref="F42:O42"/>
+    <mergeCell ref="F37:O37"/>
+    <mergeCell ref="F38:O38"/>
+    <mergeCell ref="F39:O39"/>
+    <mergeCell ref="F40:O40"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A36:N36"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="C10:O10"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="H9:O9"/>
+    <mergeCell ref="C9:E9"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A6:B6"/>
@@ -9542,45 +9473,6 @@
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="H7:O7"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="C10:O10"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="H9:O9"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A36:N36"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="F41:O41"/>
-    <mergeCell ref="F42:O42"/>
-    <mergeCell ref="F37:O37"/>
-    <mergeCell ref="F38:O38"/>
-    <mergeCell ref="F39:O39"/>
-    <mergeCell ref="F40:O40"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/(枠)◯年度一式/管理月報/実施要領報告様式_(変更).xlsx
+++ b/(枠)◯年度一式/管理月報/実施要領報告様式_(変更).xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr updateLinks="always" defaultThemeVersion="124226"/>
+  <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\ドキュメント\日報月報他\(枠)◯年度一式\管理月報\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD10E7C-F160-4B9F-9E9C-9A633807C6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10FB8270-41EA-498B-A425-E5C53C06F099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5610" yWindow="0" windowWidth="20535" windowHeight="15480" xr2:uid="{A1FB16B0-34AF-456D-9543-CB77EF9D5048}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A1FB16B0-34AF-456D-9543-CB77EF9D5048}"/>
   </bookViews>
   <sheets>
     <sheet name="別記様式１" sheetId="1" r:id="rId1"/>
@@ -3141,27 +3141,123 @@
     <xf numFmtId="183" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3177,112 +3273,67 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="185" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3293,57 +3344,6 @@
     </xf>
     <xf numFmtId="185" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3397,6 +3397,99 @@
           <cell r="E9">
             <v>2027</v>
           </cell>
+        </row>
+        <row r="13">
+          <cell r="C13"/>
+        </row>
+        <row r="14">
+          <cell r="C14"/>
+        </row>
+        <row r="15">
+          <cell r="C15"/>
+        </row>
+        <row r="16">
+          <cell r="C16"/>
+        </row>
+        <row r="17">
+          <cell r="C17"/>
+        </row>
+        <row r="18">
+          <cell r="C18"/>
+        </row>
+        <row r="19">
+          <cell r="C19"/>
+        </row>
+        <row r="20">
+          <cell r="C20"/>
+        </row>
+        <row r="21">
+          <cell r="C21"/>
+        </row>
+        <row r="22">
+          <cell r="C22"/>
+        </row>
+        <row r="23">
+          <cell r="C23"/>
+        </row>
+        <row r="24">
+          <cell r="C24"/>
+        </row>
+        <row r="25">
+          <cell r="C25"/>
+        </row>
+        <row r="26">
+          <cell r="C26"/>
+        </row>
+        <row r="27">
+          <cell r="C27"/>
+        </row>
+        <row r="28">
+          <cell r="C28"/>
+        </row>
+        <row r="29">
+          <cell r="C29"/>
+        </row>
+        <row r="30">
+          <cell r="C30"/>
+        </row>
+        <row r="31">
+          <cell r="C31"/>
+        </row>
+        <row r="32">
+          <cell r="C32"/>
+        </row>
+        <row r="33">
+          <cell r="C33"/>
+        </row>
+        <row r="34">
+          <cell r="C34"/>
+        </row>
+        <row r="35">
+          <cell r="C35"/>
+        </row>
+        <row r="36">
+          <cell r="C36"/>
+        </row>
+        <row r="37">
+          <cell r="C37"/>
+        </row>
+        <row r="38">
+          <cell r="C38"/>
+        </row>
+        <row r="39">
+          <cell r="C39"/>
+        </row>
+        <row r="40">
+          <cell r="C40"/>
+        </row>
+        <row r="41">
+          <cell r="C41"/>
+        </row>
+        <row r="42">
+          <cell r="C42"/>
+        </row>
+        <row r="43">
+          <cell r="C43"/>
         </row>
         <row r="44">
           <cell r="C44">
@@ -6201,24 +6294,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="82" t="str">
+      <c r="A1" s="114" t="str">
         <f>"令和"&amp;'[1]A-1'!$E$9-2018&amp;"年度　ごみ焼却施設維持管理状況報告書"</f>
         <v>令和9年度　ごみ焼却施設維持管理状況報告書</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="82"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
     </row>
     <row r="2" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="O2" t="s">
@@ -6226,166 +6319,166 @@
       </c>
     </row>
     <row r="3" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="115" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="93" t="s">
+      <c r="B3" s="113"/>
+      <c r="C3" s="121" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="94"/>
-      <c r="I3" s="94"/>
-      <c r="J3" s="94"/>
-      <c r="K3" s="94"/>
-      <c r="L3" s="94"/>
-      <c r="M3" s="94"/>
-      <c r="N3" s="94"/>
-      <c r="O3" s="95"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="122"/>
     </row>
     <row r="4" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="115" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="78"/>
-      <c r="C4" s="87" t="s">
+      <c r="B4" s="113"/>
+      <c r="C4" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88"/>
-      <c r="M4" s="88"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="89"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="103"/>
+      <c r="L4" s="103"/>
+      <c r="M4" s="103"/>
+      <c r="N4" s="103"/>
+      <c r="O4" s="104"/>
     </row>
     <row r="5" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="115" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="87" t="s">
+      <c r="B5" s="113"/>
+      <c r="C5" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="88"/>
-      <c r="E5" s="88"/>
-      <c r="F5" s="88"/>
-      <c r="G5" s="88"/>
-      <c r="H5" s="88"/>
-      <c r="I5" s="88"/>
-      <c r="J5" s="88"/>
-      <c r="K5" s="88"/>
-      <c r="L5" s="88"/>
-      <c r="M5" s="88"/>
-      <c r="N5" s="88"/>
-      <c r="O5" s="89"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="103"/>
+      <c r="H5" s="103"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="103"/>
+      <c r="L5" s="103"/>
+      <c r="M5" s="103"/>
+      <c r="N5" s="103"/>
+      <c r="O5" s="104"/>
     </row>
     <row r="6" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="91" t="s">
+      <c r="A6" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="92"/>
-      <c r="C6" s="90">
+      <c r="B6" s="80"/>
+      <c r="C6" s="119">
         <v>37070</v>
       </c>
-      <c r="D6" s="88"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="91" t="s">
+      <c r="D6" s="103"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="92"/>
-      <c r="H6" s="77" t="s">
+      <c r="G6" s="80"/>
+      <c r="H6" s="105" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="98"/>
-      <c r="J6" s="98"/>
-      <c r="K6" s="98"/>
-      <c r="L6" s="98"/>
-      <c r="M6" s="98"/>
-      <c r="N6" s="98"/>
-      <c r="O6" s="99"/>
+      <c r="I6" s="106"/>
+      <c r="J6" s="106"/>
+      <c r="K6" s="106"/>
+      <c r="L6" s="106"/>
+      <c r="M6" s="106"/>
+      <c r="N6" s="106"/>
+      <c r="O6" s="107"/>
       <c r="Q6" s="38"/>
     </row>
     <row r="7" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="77" t="s">
+      <c r="A7" s="105" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="78"/>
-      <c r="C7" s="84" t="s">
+      <c r="B7" s="113"/>
+      <c r="C7" s="116" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="85"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="77" t="s">
+      <c r="D7" s="117"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="78"/>
-      <c r="H7" s="77" t="s">
+      <c r="G7" s="113"/>
+      <c r="H7" s="105" t="s">
         <v>79</v>
       </c>
-      <c r="I7" s="96"/>
-      <c r="J7" s="96"/>
-      <c r="K7" s="96"/>
-      <c r="L7" s="96"/>
-      <c r="M7" s="96"/>
-      <c r="N7" s="96"/>
-      <c r="O7" s="97"/>
+      <c r="I7" s="82"/>
+      <c r="J7" s="82"/>
+      <c r="K7" s="82"/>
+      <c r="L7" s="82"/>
+      <c r="M7" s="82"/>
+      <c r="N7" s="82"/>
+      <c r="O7" s="83"/>
       <c r="Q7" s="39"/>
     </row>
     <row r="8" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="77" t="s">
+      <c r="A8" s="105" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="78"/>
-      <c r="C8" s="87" t="s">
+      <c r="B8" s="113"/>
+      <c r="C8" s="81" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="97"/>
-      <c r="H8" s="77" t="s">
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="105" t="s">
         <v>52</v>
       </c>
-      <c r="I8" s="97"/>
-      <c r="J8" s="87" t="s">
+      <c r="I8" s="83"/>
+      <c r="J8" s="81" t="s">
         <v>82</v>
       </c>
-      <c r="K8" s="96"/>
-      <c r="L8" s="96"/>
-      <c r="M8" s="96"/>
-      <c r="N8" s="96"/>
-      <c r="O8" s="97"/>
+      <c r="K8" s="82"/>
+      <c r="L8" s="82"/>
+      <c r="M8" s="82"/>
+      <c r="N8" s="82"/>
+      <c r="O8" s="83"/>
       <c r="Q8" s="38"/>
     </row>
     <row r="9" spans="1:17" s="3" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="77" t="s">
+      <c r="A9" s="105" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="98"/>
-      <c r="C9" s="87" t="s">
+      <c r="B9" s="106"/>
+      <c r="C9" s="81" t="s">
         <v>80</v>
       </c>
-      <c r="D9" s="96"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="96"/>
-      <c r="K9" s="96"/>
-      <c r="L9" s="96"/>
-      <c r="M9" s="96"/>
-      <c r="N9" s="96"/>
-      <c r="O9" s="97"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="82"/>
+      <c r="J9" s="82"/>
+      <c r="K9" s="82"/>
+      <c r="L9" s="82"/>
+      <c r="M9" s="82"/>
+      <c r="N9" s="82"/>
+      <c r="O9" s="83"/>
       <c r="Q9" s="39"/>
     </row>
     <row r="10" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.15">
@@ -6411,8 +6504,8 @@
       </c>
     </row>
     <row r="12" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="101"/>
-      <c r="B12" s="102"/>
+      <c r="A12" s="109"/>
+      <c r="B12" s="110"/>
       <c r="C12" s="4" t="s">
         <v>64</v>
       </c>
@@ -6454,10 +6547,10 @@
       </c>
     </row>
     <row r="13" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="87" t="s">
+      <c r="A13" s="81" t="s">
         <v>89</v>
       </c>
-      <c r="B13" s="89"/>
+      <c r="B13" s="104"/>
       <c r="C13" s="30">
         <f>[1]可燃!$F$43
 +[1]紙類!$K$43</f>
@@ -6524,10 +6617,10 @@
       </c>
     </row>
     <row r="14" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="100" t="s">
+      <c r="A14" s="108" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="89"/>
+      <c r="B14" s="104"/>
       <c r="C14" s="30">
         <f>SUM(C15:C17)</f>
         <v>0</v>
@@ -6768,10 +6861,10 @@
       </c>
     </row>
     <row r="18" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="103" t="s">
+      <c r="A18" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="104"/>
+      <c r="B18" s="112"/>
       <c r="C18" s="30">
         <f>SUM(C13:C14)</f>
         <v>0</v>
@@ -6832,8 +6925,8 @@
       </c>
     </row>
     <row r="21" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="101"/>
-      <c r="B21" s="102"/>
+      <c r="A21" s="109"/>
+      <c r="B21" s="110"/>
       <c r="C21" s="4" t="s">
         <v>64</v>
       </c>
@@ -6875,7 +6968,7 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="79" t="s">
+      <c r="A22" s="100" t="s">
         <v>13</v>
       </c>
       <c r="B22" s="36" t="s">
@@ -6937,7 +7030,7 @@
       <c r="S22" s="3"/>
     </row>
     <row r="23" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="80"/>
+      <c r="A23" s="101"/>
       <c r="B23" s="35" t="s">
         <v>55</v>
       </c>
@@ -6996,7 +7089,7 @@
       <c r="S23" s="3"/>
     </row>
     <row r="24" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="80"/>
+      <c r="A24" s="101"/>
       <c r="B24" s="34" t="s">
         <v>48</v>
       </c>
@@ -7056,7 +7149,7 @@
       <c r="U24" s="3"/>
     </row>
     <row r="25" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="79" t="s">
+      <c r="A25" s="100" t="s">
         <v>0</v>
       </c>
       <c r="B25" s="36" t="s">
@@ -7116,7 +7209,7 @@
       </c>
     </row>
     <row r="26" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="80"/>
+      <c r="A26" s="101"/>
       <c r="B26" s="35" t="s">
         <v>56</v>
       </c>
@@ -7174,7 +7267,7 @@
       </c>
     </row>
     <row r="27" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="80"/>
+      <c r="A27" s="101"/>
       <c r="B27" s="7" t="s">
         <v>47</v>
       </c>
@@ -7234,7 +7327,7 @@
       <c r="Q27" s="3"/>
     </row>
     <row r="28" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="80"/>
+      <c r="A28" s="101"/>
       <c r="B28" s="33" t="s">
         <v>87</v>
       </c>
@@ -7293,7 +7386,7 @@
       <c r="Q28" s="3"/>
     </row>
     <row r="29" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="81"/>
+      <c r="A29" s="102"/>
       <c r="B29" s="34" t="s">
         <v>88</v>
       </c>
@@ -7357,8 +7450,8 @@
       </c>
     </row>
     <row r="32" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="106"/>
-      <c r="B32" s="107"/>
+      <c r="A32" s="95"/>
+      <c r="B32" s="96"/>
       <c r="C32" s="4" t="s">
         <v>64</v>
       </c>
@@ -7398,10 +7491,10 @@
       <c r="O32" s="4"/>
     </row>
     <row r="33" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="79" t="s">
+      <c r="A33" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="B33" s="108" t="s">
+      <c r="B33" s="97" t="s">
         <v>20</v>
       </c>
       <c r="C33" s="12">
@@ -7457,8 +7550,8 @@
       </c>
     </row>
     <row r="34" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="80"/>
-      <c r="B34" s="109"/>
+      <c r="A34" s="101"/>
+      <c r="B34" s="98"/>
       <c r="C34" s="14" t="str">
         <f>'[1]A-1'!$H$45</f>
         <v/>
@@ -7512,8 +7605,8 @@
       </c>
     </row>
     <row r="35" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="80"/>
-      <c r="B35" s="110"/>
+      <c r="A35" s="101"/>
+      <c r="B35" s="99"/>
       <c r="C35" s="16">
         <f>'[1]A-1'!$H$47</f>
         <v>0</v>
@@ -7567,8 +7660,8 @@
       </c>
     </row>
     <row r="36" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="80"/>
-      <c r="B36" s="108" t="s">
+      <c r="A36" s="101"/>
+      <c r="B36" s="97" t="s">
         <v>21</v>
       </c>
       <c r="C36" s="26">
@@ -7624,8 +7717,8 @@
       </c>
     </row>
     <row r="37" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="80"/>
-      <c r="B37" s="109"/>
+      <c r="A37" s="101"/>
+      <c r="B37" s="98"/>
       <c r="C37" s="40" t="str">
         <f>'[1]A-1'!$L$45</f>
         <v/>
@@ -7679,8 +7772,8 @@
       </c>
     </row>
     <row r="38" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="80"/>
-      <c r="B38" s="108" t="s">
+      <c r="A38" s="101"/>
+      <c r="B38" s="97" t="s">
         <v>19</v>
       </c>
       <c r="C38" s="12">
@@ -7736,8 +7829,8 @@
       </c>
     </row>
     <row r="39" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="81"/>
-      <c r="B39" s="110"/>
+      <c r="A39" s="102"/>
+      <c r="B39" s="99"/>
       <c r="C39" s="19" t="str">
         <f>'[1]A-1'!$N$45</f>
         <v/>
@@ -7794,151 +7887,151 @@
       <c r="A40" t="s">
         <v>96</v>
       </c>
-      <c r="F40" s="115" t="s">
+      <c r="F40" s="88" t="s">
         <v>189</v>
       </c>
-      <c r="G40" s="94"/>
-      <c r="H40" s="94"/>
-      <c r="I40" s="94"/>
-      <c r="J40" s="94"/>
-      <c r="K40" s="94"/>
-      <c r="L40" s="94"/>
+      <c r="G40" s="89"/>
+      <c r="H40" s="89"/>
+      <c r="I40" s="89"/>
+      <c r="J40" s="89"/>
+      <c r="K40" s="89"/>
+      <c r="L40" s="89"/>
     </row>
     <row r="41" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41"/>
-      <c r="B41" s="105"/>
-      <c r="C41" s="113" t="s">
+      <c r="B41" s="94"/>
+      <c r="C41" s="86" t="s">
         <v>97</v>
       </c>
-      <c r="D41" s="114"/>
-      <c r="E41" s="111" t="s">
+      <c r="D41" s="87"/>
+      <c r="E41" s="79" t="s">
         <v>98</v>
       </c>
-      <c r="F41" s="92"/>
-      <c r="G41" s="113" t="s">
+      <c r="F41" s="80"/>
+      <c r="G41" s="86" t="s">
         <v>99</v>
       </c>
-      <c r="H41" s="114"/>
-      <c r="I41" s="111" t="s">
+      <c r="H41" s="87"/>
+      <c r="I41" s="79" t="s">
         <v>100</v>
       </c>
-      <c r="J41" s="92"/>
-      <c r="K41" s="111" t="s">
+      <c r="J41" s="80"/>
+      <c r="K41" s="79" t="s">
         <v>101</v>
       </c>
-      <c r="L41" s="92"/>
-      <c r="M41" s="111" t="s">
+      <c r="L41" s="80"/>
+      <c r="M41" s="79" t="s">
         <v>185</v>
       </c>
-      <c r="N41" s="92"/>
+      <c r="N41" s="80"/>
     </row>
     <row r="42" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B42" s="105"/>
-      <c r="C42" s="116" t="s">
+      <c r="B42" s="94"/>
+      <c r="C42" s="90" t="s">
         <v>102</v>
       </c>
-      <c r="D42" s="117"/>
-      <c r="E42" s="75" t="s">
+      <c r="D42" s="91"/>
+      <c r="E42" s="84" t="s">
         <v>103</v>
       </c>
-      <c r="F42" s="76"/>
-      <c r="G42" s="116" t="s">
+      <c r="F42" s="85"/>
+      <c r="G42" s="90" t="s">
         <v>104</v>
       </c>
-      <c r="H42" s="117"/>
-      <c r="I42" s="75" t="s">
+      <c r="H42" s="91"/>
+      <c r="I42" s="84" t="s">
         <v>105</v>
       </c>
-      <c r="J42" s="76"/>
-      <c r="K42" s="75" t="s">
+      <c r="J42" s="85"/>
+      <c r="K42" s="84" t="s">
         <v>106</v>
       </c>
-      <c r="L42" s="76"/>
-      <c r="M42" s="118" t="s">
+      <c r="L42" s="85"/>
+      <c r="M42" s="92" t="s">
         <v>186</v>
       </c>
-      <c r="N42" s="119"/>
+      <c r="N42" s="93"/>
     </row>
     <row r="43" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="C43" s="112"/>
-      <c r="D43" s="112"/>
-      <c r="E43" s="112">
+      <c r="C43" s="75"/>
+      <c r="D43" s="75"/>
+      <c r="E43" s="75">
         <v>1E-3</v>
       </c>
-      <c r="F43" s="112"/>
-      <c r="G43" s="112">
+      <c r="F43" s="75"/>
+      <c r="G43" s="75">
         <v>16</v>
       </c>
-      <c r="H43" s="112"/>
-      <c r="I43" s="112">
+      <c r="H43" s="75"/>
+      <c r="I43" s="75">
         <v>0.03</v>
       </c>
-      <c r="J43" s="112"/>
-      <c r="K43" s="112">
+      <c r="J43" s="75"/>
+      <c r="K43" s="75">
         <v>86</v>
       </c>
-      <c r="L43" s="112"/>
-      <c r="M43" s="112">
+      <c r="L43" s="75"/>
+      <c r="M43" s="75">
         <v>0.28999999999999998</v>
       </c>
-      <c r="N43" s="112"/>
+      <c r="N43" s="75"/>
     </row>
     <row r="44" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="C44" s="112" t="s">
+      <c r="C44" s="75" t="s">
         <v>180</v>
       </c>
-      <c r="D44" s="112"/>
-      <c r="E44" s="112" t="s">
+      <c r="D44" s="75"/>
+      <c r="E44" s="75" t="s">
         <v>181</v>
       </c>
-      <c r="F44" s="112"/>
-      <c r="G44" s="112" t="s">
+      <c r="F44" s="75"/>
+      <c r="G44" s="75" t="s">
         <v>182</v>
       </c>
-      <c r="H44" s="112"/>
-      <c r="I44" s="112" t="s">
+      <c r="H44" s="75"/>
+      <c r="I44" s="75" t="s">
         <v>191</v>
       </c>
-      <c r="J44" s="112"/>
-      <c r="K44" s="112" t="s">
+      <c r="J44" s="75"/>
+      <c r="K44" s="75" t="s">
         <v>183</v>
       </c>
-      <c r="L44" s="112"/>
-      <c r="M44" s="112" t="s">
+      <c r="L44" s="75"/>
+      <c r="M44" s="75" t="s">
         <v>190</v>
       </c>
-      <c r="N44" s="112"/>
+      <c r="N44" s="75"/>
     </row>
     <row r="45" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
         <v>159</v>
       </c>
-      <c r="E45" s="121" t="s">
+      <c r="E45" s="77" t="s">
         <v>187</v>
       </c>
-      <c r="F45" s="122"/>
-      <c r="G45" s="122"/>
-      <c r="H45" s="122"/>
-      <c r="I45" s="122"/>
-      <c r="J45" s="122"/>
-      <c r="K45" s="122"/>
+      <c r="F45" s="78"/>
+      <c r="G45" s="78"/>
+      <c r="H45" s="78"/>
+      <c r="I45" s="78"/>
+      <c r="J45" s="78"/>
+      <c r="K45" s="78"/>
     </row>
     <row r="46" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="64"/>
-      <c r="C46" s="120" t="s">
+      <c r="C46" s="76" t="s">
         <v>160</v>
       </c>
-      <c r="D46" s="112"/>
-      <c r="E46" s="120" t="s">
+      <c r="D46" s="75"/>
+      <c r="E46" s="76" t="s">
         <v>161</v>
       </c>
-      <c r="F46" s="112"/>
+      <c r="F46" s="75"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
@@ -7949,10 +8042,10 @@
       <c r="B47" s="63" t="s">
         <v>162</v>
       </c>
-      <c r="C47" s="112"/>
-      <c r="D47" s="112"/>
-      <c r="E47" s="112"/>
-      <c r="F47" s="112"/>
+      <c r="C47" s="75"/>
+      <c r="D47" s="75"/>
+      <c r="E47" s="75"/>
+      <c r="F47" s="75"/>
       <c r="L47" s="70"/>
       <c r="M47" s="70"/>
     </row>
@@ -8170,21 +8263,39 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="E45:K45"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A25:A29"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C5:O5"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C3:O3"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H7:O7"/>
+    <mergeCell ref="C4:O4"/>
+    <mergeCell ref="H6:O6"/>
+    <mergeCell ref="J8:O8"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A33:A39"/>
+    <mergeCell ref="B33:B35"/>
     <mergeCell ref="I41:J41"/>
     <mergeCell ref="G43:H43"/>
     <mergeCell ref="C8:G8"/>
@@ -8201,39 +8312,21 @@
     <mergeCell ref="M41:N41"/>
     <mergeCell ref="M42:N42"/>
     <mergeCell ref="M43:N43"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="A33:A39"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="C4:O4"/>
-    <mergeCell ref="H6:O6"/>
-    <mergeCell ref="J8:O8"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A25:A29"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C5:O5"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C3:O3"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H7:O7"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E45:K45"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -8259,24 +8352,24 @@
       <c r="A1"/>
     </row>
     <row r="2" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="82" t="str">
+      <c r="A2" s="114" t="str">
         <f>"令和"&amp;'[1]A-1'!$E$9-2018&amp;"年度　最終処分場維持管理状況報告書"</f>
         <v>令和9年度　最終処分場維持管理状況報告書</v>
       </c>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="J2" s="82"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="82"/>
-      <c r="M2" s="82"/>
-      <c r="N2" s="82"/>
-      <c r="O2" s="82"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
+      <c r="O2" s="114"/>
     </row>
     <row r="3" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="M3"/>
@@ -8285,167 +8378,167 @@
       </c>
     </row>
     <row r="4" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="115" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="78"/>
-      <c r="C4" s="93" t="s">
+      <c r="B4" s="113"/>
+      <c r="C4" s="121" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="94"/>
-      <c r="I4" s="94"/>
-      <c r="J4" s="94"/>
-      <c r="K4" s="94"/>
-      <c r="L4" s="94"/>
-      <c r="M4" s="94"/>
-      <c r="N4" s="94"/>
-      <c r="O4" s="95"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="89"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="122"/>
     </row>
     <row r="5" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="115" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="87" t="s">
+      <c r="B5" s="113"/>
+      <c r="C5" s="81" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="88"/>
-      <c r="E5" s="88"/>
-      <c r="F5" s="88"/>
-      <c r="G5" s="88"/>
-      <c r="H5" s="88"/>
-      <c r="I5" s="88"/>
-      <c r="J5" s="88"/>
-      <c r="K5" s="88"/>
-      <c r="L5" s="88"/>
-      <c r="M5" s="88"/>
-      <c r="N5" s="88"/>
-      <c r="O5" s="89"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="103"/>
+      <c r="H5" s="103"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="103"/>
+      <c r="L5" s="103"/>
+      <c r="M5" s="103"/>
+      <c r="N5" s="103"/>
+      <c r="O5" s="104"/>
     </row>
     <row r="6" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="115" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="78"/>
-      <c r="C6" s="87" t="s">
+      <c r="B6" s="113"/>
+      <c r="C6" s="81" t="s">
         <v>201</v>
       </c>
-      <c r="D6" s="88"/>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="88"/>
-      <c r="K6" s="88"/>
-      <c r="L6" s="88"/>
-      <c r="M6" s="88"/>
-      <c r="N6" s="88"/>
-      <c r="O6" s="89"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="103"/>
+      <c r="G6" s="103"/>
+      <c r="H6" s="103"/>
+      <c r="I6" s="103"/>
+      <c r="J6" s="103"/>
+      <c r="K6" s="103"/>
+      <c r="L6" s="103"/>
+      <c r="M6" s="103"/>
+      <c r="N6" s="103"/>
+      <c r="O6" s="104"/>
     </row>
     <row r="7" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="91" t="s">
+      <c r="A7" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="92"/>
-      <c r="C7" s="123">
+      <c r="B7" s="80"/>
+      <c r="C7" s="140">
         <v>42527</v>
       </c>
-      <c r="D7" s="124"/>
-      <c r="E7" s="125"/>
-      <c r="F7" s="91" t="s">
+      <c r="D7" s="141"/>
+      <c r="E7" s="142"/>
+      <c r="F7" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="92"/>
-      <c r="H7" s="77" t="s">
+      <c r="G7" s="80"/>
+      <c r="H7" s="105" t="s">
         <v>195</v>
       </c>
-      <c r="I7" s="98"/>
-      <c r="J7" s="98"/>
-      <c r="K7" s="98"/>
-      <c r="L7" s="98"/>
-      <c r="M7" s="98"/>
-      <c r="N7" s="98"/>
-      <c r="O7" s="99"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="106"/>
+      <c r="K7" s="106"/>
+      <c r="L7" s="106"/>
+      <c r="M7" s="106"/>
+      <c r="N7" s="106"/>
+      <c r="O7" s="107"/>
     </row>
     <row r="8" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="120" t="s">
+      <c r="A8" s="76" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="112"/>
-      <c r="C8" s="84" t="s">
+      <c r="B8" s="75"/>
+      <c r="C8" s="116" t="s">
         <v>196</v>
       </c>
-      <c r="D8" s="85"/>
-      <c r="E8" s="86"/>
-      <c r="F8" s="120" t="s">
+      <c r="D8" s="117"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="112"/>
-      <c r="H8" s="77" t="s">
+      <c r="G8" s="75"/>
+      <c r="H8" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="I8" s="128"/>
-      <c r="J8" s="78"/>
-      <c r="K8" s="120" t="s">
+      <c r="I8" s="138"/>
+      <c r="J8" s="113"/>
+      <c r="K8" s="76" t="s">
         <v>43</v>
       </c>
-      <c r="L8" s="112"/>
-      <c r="M8" s="77" t="s">
+      <c r="L8" s="75"/>
+      <c r="M8" s="105" t="s">
         <v>197</v>
       </c>
-      <c r="N8" s="128"/>
-      <c r="O8" s="78"/>
+      <c r="N8" s="138"/>
+      <c r="O8" s="113"/>
     </row>
     <row r="9" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="120" t="s">
+      <c r="A9" s="76" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="112"/>
-      <c r="C9" s="84" t="s">
+      <c r="B9" s="75"/>
+      <c r="C9" s="116" t="s">
         <v>199</v>
       </c>
-      <c r="D9" s="85"/>
-      <c r="E9" s="86"/>
-      <c r="F9" s="120" t="s">
+      <c r="D9" s="117"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="112"/>
-      <c r="H9" s="87" t="s">
+      <c r="G9" s="75"/>
+      <c r="H9" s="81" t="s">
         <v>198</v>
       </c>
-      <c r="I9" s="88"/>
-      <c r="J9" s="88"/>
-      <c r="K9" s="96"/>
-      <c r="L9" s="96"/>
-      <c r="M9" s="96"/>
-      <c r="N9" s="96"/>
-      <c r="O9" s="97"/>
+      <c r="I9" s="103"/>
+      <c r="J9" s="103"/>
+      <c r="K9" s="82"/>
+      <c r="L9" s="82"/>
+      <c r="M9" s="82"/>
+      <c r="N9" s="82"/>
+      <c r="O9" s="83"/>
     </row>
     <row r="10" spans="1:15" s="3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="77" t="s">
+      <c r="A10" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="98"/>
-      <c r="C10" s="93" t="s">
+      <c r="B10" s="106"/>
+      <c r="C10" s="121" t="s">
         <v>200</v>
       </c>
-      <c r="D10" s="115"/>
-      <c r="E10" s="115"/>
-      <c r="F10" s="115"/>
-      <c r="G10" s="115"/>
-      <c r="H10" s="115"/>
-      <c r="I10" s="115"/>
-      <c r="J10" s="115"/>
-      <c r="K10" s="115"/>
-      <c r="L10" s="115"/>
-      <c r="M10" s="115"/>
-      <c r="N10" s="115"/>
-      <c r="O10" s="129"/>
+      <c r="D10" s="88"/>
+      <c r="E10" s="88"/>
+      <c r="F10" s="88"/>
+      <c r="G10" s="88"/>
+      <c r="H10" s="88"/>
+      <c r="I10" s="88"/>
+      <c r="J10" s="88"/>
+      <c r="K10" s="88"/>
+      <c r="L10" s="88"/>
+      <c r="M10" s="88"/>
+      <c r="N10" s="88"/>
+      <c r="O10" s="139"/>
     </row>
     <row r="11" spans="1:15" s="3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2"/>
@@ -8461,8 +8554,8 @@
       </c>
     </row>
     <row r="13" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="101"/>
-      <c r="B13" s="102"/>
+      <c r="A13" s="109"/>
+      <c r="B13" s="110"/>
       <c r="C13" s="4" t="s">
         <v>12</v>
       </c>
@@ -8504,10 +8597,10 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="100" t="s">
+      <c r="A14" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="89"/>
+      <c r="B14" s="104"/>
       <c r="C14" s="30">
         <f>SUM(C15:C17)</f>
         <v>0</v>
@@ -8760,10 +8853,10 @@
       </c>
     </row>
     <row r="18" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="87" t="s">
+      <c r="A18" s="81" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="97"/>
+      <c r="B18" s="83"/>
       <c r="C18" s="10">
         <f>'[1]B-1'!$H$45</f>
         <v>0</v>
@@ -8818,10 +8911,10 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="132" t="s">
+      <c r="A19" s="131" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="133"/>
+      <c r="B19" s="132"/>
       <c r="C19" s="25">
         <f>SUM(C15:C18)</f>
         <v>0</v>
@@ -8876,10 +8969,10 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="134" t="s">
+      <c r="A20" s="133" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="135"/>
+      <c r="B20" s="134"/>
       <c r="C20" s="46">
         <f>ROUND(C19*1.5,1)</f>
         <v>0</v>
@@ -8934,10 +9027,10 @@
       </c>
     </row>
     <row r="21" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="136" t="s">
+      <c r="A21" s="135" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="104"/>
+      <c r="B21" s="112"/>
       <c r="C21" s="47">
         <f>'[1]B-1'!$I$45</f>
         <v>0</v>
@@ -8992,10 +9085,10 @@
       </c>
     </row>
     <row r="22" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="136" t="s">
+      <c r="A22" s="135" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="104"/>
+      <c r="B22" s="112"/>
       <c r="C22" s="47">
         <f>SUM(C20:C21)</f>
         <v>0</v>
@@ -9054,13 +9147,13 @@
         <v>188</v>
       </c>
       <c r="B23"/>
-      <c r="D23" s="131"/>
-      <c r="E23" s="131"/>
-      <c r="K23" s="126"/>
-      <c r="L23" s="127"/>
-      <c r="M23" s="127"/>
-      <c r="N23" s="126"/>
-      <c r="O23" s="127"/>
+      <c r="D23" s="130"/>
+      <c r="E23" s="130"/>
+      <c r="K23" s="136"/>
+      <c r="L23" s="137"/>
+      <c r="M23" s="137"/>
+      <c r="N23" s="136"/>
+      <c r="O23" s="137"/>
     </row>
     <row r="24" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="25" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -9069,8 +9162,8 @@
       </c>
     </row>
     <row r="26" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="106"/>
-      <c r="B26" s="107"/>
+      <c r="A26" s="95"/>
+      <c r="B26" s="96"/>
       <c r="C26" s="4" t="s">
         <v>12</v>
       </c>
@@ -9112,7 +9205,7 @@
       </c>
     </row>
     <row r="27" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="130" t="s">
+      <c r="A27" s="129" t="s">
         <v>28</v>
       </c>
       <c r="B27" s="11" t="s">
@@ -9136,7 +9229,7 @@
       </c>
     </row>
     <row r="28" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="80"/>
+      <c r="A28" s="101"/>
       <c r="B28" s="28" t="s">
         <v>36</v>
       </c>
@@ -9158,7 +9251,7 @@
       </c>
     </row>
     <row r="29" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="80"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="27" t="s">
         <v>38</v>
       </c>
@@ -9180,7 +9273,7 @@
       </c>
     </row>
     <row r="30" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="130" t="s">
+      <c r="A30" s="129" t="s">
         <v>29</v>
       </c>
       <c r="B30" s="11" t="s">
@@ -9204,7 +9297,7 @@
       </c>
     </row>
     <row r="31" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="80"/>
+      <c r="A31" s="101"/>
       <c r="B31" s="28" t="s">
         <v>36</v>
       </c>
@@ -9226,7 +9319,7 @@
       </c>
     </row>
     <row r="32" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="81"/>
+      <c r="A32" s="102"/>
       <c r="B32" s="55" t="s">
         <v>38</v>
       </c>
@@ -9260,139 +9353,139 @@
       <c r="I35" s="18"/>
     </row>
     <row r="36" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="138" t="s">
+      <c r="A36" s="128" t="s">
         <v>92</v>
       </c>
-      <c r="B36" s="138"/>
-      <c r="C36" s="138"/>
-      <c r="D36" s="138"/>
-      <c r="E36" s="138"/>
-      <c r="F36" s="138"/>
-      <c r="G36" s="138"/>
-      <c r="H36" s="138"/>
-      <c r="I36" s="138"/>
-      <c r="J36" s="138"/>
-      <c r="K36" s="138"/>
-      <c r="L36" s="138"/>
-      <c r="M36" s="138"/>
-      <c r="N36" s="138"/>
+      <c r="B36" s="128"/>
+      <c r="C36" s="128"/>
+      <c r="D36" s="128"/>
+      <c r="E36" s="128"/>
+      <c r="F36" s="128"/>
+      <c r="G36" s="128"/>
+      <c r="H36" s="128"/>
+      <c r="I36" s="128"/>
+      <c r="J36" s="128"/>
+      <c r="K36" s="128"/>
+      <c r="L36" s="128"/>
+      <c r="M36" s="128"/>
+      <c r="N36" s="128"/>
       <c r="O36" s="57"/>
     </row>
     <row r="37" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="120" t="s">
+      <c r="A37" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="B37" s="112"/>
-      <c r="C37" s="120" t="s">
+      <c r="B37" s="75"/>
+      <c r="C37" s="76" t="s">
         <v>93</v>
       </c>
-      <c r="D37" s="112"/>
-      <c r="E37" s="112"/>
-      <c r="F37" s="120" t="s">
+      <c r="D37" s="75"/>
+      <c r="E37" s="75"/>
+      <c r="F37" s="76" t="s">
         <v>94</v>
       </c>
-      <c r="G37" s="120"/>
-      <c r="H37" s="120"/>
-      <c r="I37" s="120"/>
-      <c r="J37" s="120"/>
-      <c r="K37" s="120"/>
-      <c r="L37" s="120"/>
-      <c r="M37" s="120"/>
-      <c r="N37" s="120"/>
-      <c r="O37" s="120"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="76"/>
+      <c r="I37" s="76"/>
+      <c r="J37" s="76"/>
+      <c r="K37" s="76"/>
+      <c r="L37" s="76"/>
+      <c r="M37" s="76"/>
+      <c r="N37" s="76"/>
+      <c r="O37" s="76"/>
     </row>
     <row r="38" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="137">
+      <c r="A38" s="127">
         <v>45036</v>
       </c>
-      <c r="B38" s="137"/>
-      <c r="C38" s="139"/>
-      <c r="D38" s="139"/>
-      <c r="E38" s="139"/>
-      <c r="F38" s="140" t="s">
+      <c r="B38" s="127"/>
+      <c r="C38" s="123"/>
+      <c r="D38" s="123"/>
+      <c r="E38" s="123"/>
+      <c r="F38" s="124" t="s">
         <v>179</v>
       </c>
-      <c r="G38" s="141"/>
-      <c r="H38" s="141"/>
-      <c r="I38" s="141"/>
-      <c r="J38" s="141"/>
-      <c r="K38" s="141"/>
-      <c r="L38" s="141"/>
-      <c r="M38" s="141"/>
-      <c r="N38" s="141"/>
-      <c r="O38" s="142"/>
+      <c r="G38" s="125"/>
+      <c r="H38" s="125"/>
+      <c r="I38" s="125"/>
+      <c r="J38" s="125"/>
+      <c r="K38" s="125"/>
+      <c r="L38" s="125"/>
+      <c r="M38" s="125"/>
+      <c r="N38" s="125"/>
+      <c r="O38" s="126"/>
     </row>
     <row r="39" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="137">
+      <c r="A39" s="127">
         <v>45108</v>
       </c>
-      <c r="B39" s="137"/>
-      <c r="C39" s="139"/>
-      <c r="D39" s="139"/>
-      <c r="E39" s="139"/>
-      <c r="F39" s="140" t="s">
+      <c r="B39" s="127"/>
+      <c r="C39" s="123"/>
+      <c r="D39" s="123"/>
+      <c r="E39" s="123"/>
+      <c r="F39" s="124" t="s">
         <v>179</v>
       </c>
-      <c r="G39" s="141"/>
-      <c r="H39" s="141"/>
-      <c r="I39" s="141"/>
-      <c r="J39" s="141"/>
-      <c r="K39" s="141"/>
-      <c r="L39" s="141"/>
-      <c r="M39" s="141"/>
-      <c r="N39" s="141"/>
-      <c r="O39" s="142"/>
+      <c r="G39" s="125"/>
+      <c r="H39" s="125"/>
+      <c r="I39" s="125"/>
+      <c r="J39" s="125"/>
+      <c r="K39" s="125"/>
+      <c r="L39" s="125"/>
+      <c r="M39" s="125"/>
+      <c r="N39" s="125"/>
+      <c r="O39" s="126"/>
     </row>
     <row r="40" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="120"/>
-      <c r="B40" s="120"/>
-      <c r="C40" s="139"/>
-      <c r="D40" s="139"/>
-      <c r="E40" s="139"/>
-      <c r="F40" s="139"/>
-      <c r="G40" s="139"/>
-      <c r="H40" s="139"/>
-      <c r="I40" s="139"/>
-      <c r="J40" s="139"/>
-      <c r="K40" s="139"/>
-      <c r="L40" s="139"/>
-      <c r="M40" s="139"/>
-      <c r="N40" s="139"/>
-      <c r="O40" s="139"/>
+      <c r="A40" s="76"/>
+      <c r="B40" s="76"/>
+      <c r="C40" s="123"/>
+      <c r="D40" s="123"/>
+      <c r="E40" s="123"/>
+      <c r="F40" s="123"/>
+      <c r="G40" s="123"/>
+      <c r="H40" s="123"/>
+      <c r="I40" s="123"/>
+      <c r="J40" s="123"/>
+      <c r="K40" s="123"/>
+      <c r="L40" s="123"/>
+      <c r="M40" s="123"/>
+      <c r="N40" s="123"/>
+      <c r="O40" s="123"/>
     </row>
     <row r="41" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="120"/>
-      <c r="B41" s="120"/>
-      <c r="C41" s="139"/>
-      <c r="D41" s="139"/>
-      <c r="E41" s="139"/>
-      <c r="F41" s="139"/>
-      <c r="G41" s="139"/>
-      <c r="H41" s="139"/>
-      <c r="I41" s="139"/>
-      <c r="J41" s="139"/>
-      <c r="K41" s="139"/>
-      <c r="L41" s="139"/>
-      <c r="M41" s="139"/>
-      <c r="N41" s="139"/>
-      <c r="O41" s="139"/>
+      <c r="A41" s="76"/>
+      <c r="B41" s="76"/>
+      <c r="C41" s="123"/>
+      <c r="D41" s="123"/>
+      <c r="E41" s="123"/>
+      <c r="F41" s="123"/>
+      <c r="G41" s="123"/>
+      <c r="H41" s="123"/>
+      <c r="I41" s="123"/>
+      <c r="J41" s="123"/>
+      <c r="K41" s="123"/>
+      <c r="L41" s="123"/>
+      <c r="M41" s="123"/>
+      <c r="N41" s="123"/>
+      <c r="O41" s="123"/>
     </row>
     <row r="42" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="120"/>
-      <c r="B42" s="120"/>
-      <c r="C42" s="139"/>
-      <c r="D42" s="139"/>
-      <c r="E42" s="139"/>
-      <c r="F42" s="139"/>
-      <c r="G42" s="139"/>
-      <c r="H42" s="139"/>
-      <c r="I42" s="139"/>
-      <c r="J42" s="139"/>
-      <c r="K42" s="139"/>
-      <c r="L42" s="139"/>
-      <c r="M42" s="139"/>
-      <c r="N42" s="139"/>
-      <c r="O42" s="139"/>
+      <c r="A42" s="76"/>
+      <c r="B42" s="76"/>
+      <c r="C42" s="123"/>
+      <c r="D42" s="123"/>
+      <c r="E42" s="123"/>
+      <c r="F42" s="123"/>
+      <c r="G42" s="123"/>
+      <c r="H42" s="123"/>
+      <c r="I42" s="123"/>
+      <c r="J42" s="123"/>
+      <c r="K42" s="123"/>
+      <c r="L42" s="123"/>
+      <c r="M42" s="123"/>
+      <c r="N42" s="123"/>
+      <c r="O42" s="123"/>
     </row>
     <row r="43" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43"/>
@@ -9418,45 +9511,6 @@
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="F41:O41"/>
-    <mergeCell ref="F42:O42"/>
-    <mergeCell ref="F37:O37"/>
-    <mergeCell ref="F38:O38"/>
-    <mergeCell ref="F39:O39"/>
-    <mergeCell ref="F40:O40"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A36:N36"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="C10:O10"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="H9:O9"/>
-    <mergeCell ref="C9:E9"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A6:B6"/>
@@ -9473,6 +9527,45 @@
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="H7:O7"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="C10:O10"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="H9:O9"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A36:N36"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="F41:O41"/>
+    <mergeCell ref="F42:O42"/>
+    <mergeCell ref="F37:O37"/>
+    <mergeCell ref="F38:O38"/>
+    <mergeCell ref="F39:O39"/>
+    <mergeCell ref="F40:O40"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
